--- a/data/01_systematic_review/Full_text_FinalDecisions.xlsx
+++ b/data/01_systematic_review/Full_text_FinalDecisions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\morann\Dropbox\_Project_AST_birdmeta\_Screening records\screening records ready for publication\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\morann\Dropbox\_Project_AST_birdmeta\Screening records compiled_20261025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D23B1D-C7AF-45F9-A148-C14AECE48FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C27D8D-49D6-43A3-BD11-3D84DBF9C293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{FBF6B3D8-95F4-4F81-9E7F-416B724FDE99}"/>
+    <workbookView xWindow="-7770" yWindow="-16297" windowWidth="28995" windowHeight="15675" xr2:uid="{FBF6B3D8-95F4-4F81-9E7F-416B724FDE99}"/>
   </bookViews>
   <sheets>
     <sheet name="rayyan_full_text_screening_expo" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2284" uniqueCount="854">
   <si>
     <t>Paper.ID</t>
   </si>
@@ -2586,6 +2586,15 @@
   </si>
   <si>
     <t>[NPM: published version of included thesis 138813552, previously unidentified duplicate in the fulltext database]</t>
+  </si>
+  <si>
+    <t>Data_included_in analysis</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -3052,9 +3061,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3430,29 +3438,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6917D177-D7A8-4E73-9015-BD48DE3FD09F}">
-  <dimension ref="A1:X120"/>
+  <dimension ref="A1:Y120"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.25" customWidth="1"/>
+    <col min="3" max="3" width="65.33203125" customWidth="1"/>
     <col min="8" max="8" width="30.9140625" bestFit="1" customWidth="1"/>
     <col min="11" max="18" width="14" customWidth="1"/>
     <col min="20" max="20" width="20.08203125" customWidth="1"/>
     <col min="21" max="21" width="27.58203125" customWidth="1"/>
     <col min="22" max="22" width="21.58203125" customWidth="1"/>
-    <col min="24" max="24" width="18.75" customWidth="1"/>
-    <col min="28" max="28" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.08203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.75" customWidth="1"/>
+    <col min="29" max="29" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -3513,107 +3522,107 @@
         <v>820</v>
       </c>
       <c r="W1" t="s">
+        <v>851</v>
+      </c>
+      <c r="X1" t="s">
         <v>17</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>806</v>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>138812525</v>
       </c>
       <c r="B2" t="s">
-        <v>812</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="D2" t="s">
-        <v>812</v>
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F2" t="s">
-        <v>812</v>
+        <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>812</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>815</v>
+        <v>38</v>
       </c>
       <c r="I2" t="s">
-        <v>812</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>812</v>
+        <v>39</v>
       </c>
       <c r="K2" t="s">
-        <v>812</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>812</v>
+        <v>30</v>
       </c>
       <c r="M2" t="s">
-        <v>812</v>
+        <v>28</v>
       </c>
       <c r="N2" t="s">
-        <v>812</v>
+        <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>812</v>
+        <v>28</v>
       </c>
       <c r="P2" t="s">
-        <v>812</v>
+        <v>28</v>
       </c>
       <c r="Q2" t="s">
-        <v>812</v>
+        <v>41</v>
       </c>
       <c r="R2" t="s">
-        <v>812</v>
+        <v>28</v>
       </c>
       <c r="S2" t="s">
-        <v>812</v>
-      </c>
-      <c r="T2" t="s">
-        <v>812</v>
+        <v>42</v>
       </c>
       <c r="U2" t="s">
         <v>42</v>
       </c>
-      <c r="V2" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W2" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>138812525</v>
+        <v>138812527</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
       </c>
       <c r="E3">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="I3" t="s">
         <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="K3" t="s">
         <v>28</v>
@@ -3634,7 +3643,7 @@
         <v>28</v>
       </c>
       <c r="Q3" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="R3" t="s">
         <v>28</v>
@@ -3645,37 +3654,40 @@
       <c r="U3" t="s">
         <v>42</v>
       </c>
-      <c r="X3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W3" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>138812527</v>
+        <v>138812528</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>61</v>
       </c>
       <c r="E4">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="H4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
         <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K4" t="s">
         <v>28</v>
@@ -3696,7 +3708,7 @@
         <v>28</v>
       </c>
       <c r="Q4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="R4" t="s">
         <v>28</v>
@@ -3707,37 +3719,40 @@
       <c r="U4" t="s">
         <v>42</v>
       </c>
-      <c r="X4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W4" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>138812528</v>
+        <v>138812529</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>69</v>
       </c>
       <c r="E5">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I5" t="s">
         <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K5" t="s">
         <v>28</v>
@@ -3758,7 +3773,7 @@
         <v>28</v>
       </c>
       <c r="Q5" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="R5" t="s">
         <v>28</v>
@@ -3769,37 +3784,40 @@
       <c r="U5" t="s">
         <v>42</v>
       </c>
-      <c r="X5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W5" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>138812529</v>
+        <v>138812531</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>69</v>
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>83</v>
       </c>
       <c r="E6">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="I6" t="s">
         <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="K6" t="s">
         <v>28</v>
@@ -3831,37 +3849,40 @@
       <c r="U6" t="s">
         <v>42</v>
       </c>
-      <c r="X6" t="s">
+      <c r="W6" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>138812531</v>
+        <v>138812532</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
       </c>
       <c r="E7">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G7" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
         <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K7" t="s">
         <v>28</v>
@@ -3882,7 +3903,7 @@
         <v>28</v>
       </c>
       <c r="Q7" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="R7" t="s">
         <v>28</v>
@@ -3893,37 +3914,40 @@
       <c r="U7" t="s">
         <v>42</v>
       </c>
-      <c r="X7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W7" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>138812532</v>
+        <v>138812533</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
+      </c>
+      <c r="C8" t="s">
+        <v>97</v>
       </c>
       <c r="E8">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F8" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G8" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="H8" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I8" t="s">
         <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="K8" t="s">
         <v>28</v>
@@ -3931,9 +3955,6 @@
       <c r="L8" t="s">
         <v>30</v>
       </c>
-      <c r="M8" t="s">
-        <v>28</v>
-      </c>
       <c r="N8" t="s">
         <v>28</v>
       </c>
@@ -3944,7 +3965,7 @@
         <v>28</v>
       </c>
       <c r="Q8" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="R8" t="s">
         <v>28</v>
@@ -3955,37 +3976,40 @@
       <c r="U8" t="s">
         <v>42</v>
       </c>
-      <c r="X8" t="s">
+      <c r="W8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y8" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>138812533</v>
+        <v>138812535</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
+      </c>
+      <c r="C9" t="s">
+        <v>111</v>
       </c>
       <c r="E9">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="G9" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="H9" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J9" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="K9" t="s">
         <v>28</v>
@@ -3993,6 +4017,9 @@
       <c r="L9" t="s">
         <v>30</v>
       </c>
+      <c r="M9" t="s">
+        <v>28</v>
+      </c>
       <c r="N9" t="s">
         <v>28</v>
       </c>
@@ -4003,7 +4030,7 @@
         <v>28</v>
       </c>
       <c r="Q9" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="R9" t="s">
         <v>28</v>
@@ -4014,37 +4041,40 @@
       <c r="U9" t="s">
         <v>42</v>
       </c>
+      <c r="W9" t="s">
+        <v>852</v>
+      </c>
       <c r="X9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>138812535</v>
+        <v>138812536</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
+      </c>
+      <c r="C10" t="s">
+        <v>120</v>
       </c>
       <c r="E10">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="F10" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G10" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H10" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I10" t="s">
         <v>114</v>
       </c>
       <c r="J10" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="K10" t="s">
         <v>28</v>
@@ -4065,7 +4095,7 @@
         <v>28</v>
       </c>
       <c r="Q10" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="R10" t="s">
         <v>28</v>
@@ -4077,36 +4107,39 @@
         <v>42</v>
       </c>
       <c r="W10" t="s">
+        <v>852</v>
+      </c>
+      <c r="X10" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>138812536</v>
+        <v>138812540</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>120</v>
+        <v>147</v>
+      </c>
+      <c r="C11" t="s">
+        <v>148</v>
       </c>
       <c r="E11">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="F11" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="G11" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="H11" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="I11" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="K11" t="s">
         <v>28</v>
@@ -4127,7 +4160,7 @@
         <v>28</v>
       </c>
       <c r="Q11" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="R11" t="s">
         <v>28</v>
@@ -4139,36 +4172,39 @@
         <v>42</v>
       </c>
       <c r="W11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+        <v>852</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>138812540</v>
+        <v>138812542</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>148</v>
+        <v>162</v>
+      </c>
+      <c r="C12" t="s">
+        <v>163</v>
       </c>
       <c r="E12">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F12" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="G12" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="H12" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="I12" t="s">
         <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="K12" t="s">
         <v>28</v>
@@ -4189,7 +4225,7 @@
         <v>28</v>
       </c>
       <c r="Q12" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="R12" t="s">
         <v>28</v>
@@ -4200,37 +4236,40 @@
       <c r="U12" t="s">
         <v>42</v>
       </c>
-      <c r="X12" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W12" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>138812542</v>
+        <v>138812544</v>
       </c>
       <c r="B13" t="s">
-        <v>162</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>163</v>
+        <v>178</v>
+      </c>
+      <c r="C13" t="s">
+        <v>179</v>
       </c>
       <c r="E13">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="F13" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="G13" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="H13" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="I13" t="s">
         <v>25</v>
       </c>
       <c r="J13" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="K13" t="s">
         <v>28</v>
@@ -4251,7 +4290,7 @@
         <v>28</v>
       </c>
       <c r="Q13" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="R13" t="s">
         <v>28</v>
@@ -4262,37 +4301,40 @@
       <c r="U13" t="s">
         <v>42</v>
       </c>
-      <c r="X13" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W13" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>138812544</v>
+        <v>138812547</v>
       </c>
       <c r="B14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
+      </c>
+      <c r="C14" t="s">
+        <v>194</v>
       </c>
       <c r="E14">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="F14" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="G14" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="H14" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="I14" t="s">
         <v>25</v>
       </c>
       <c r="J14" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="K14" t="s">
         <v>28</v>
@@ -4313,7 +4355,7 @@
         <v>28</v>
       </c>
       <c r="Q14" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
       <c r="R14" t="s">
         <v>28</v>
@@ -4324,37 +4366,40 @@
       <c r="U14" t="s">
         <v>42</v>
       </c>
-      <c r="X14" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W14" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>138812547</v>
+        <v>138812549</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
+      </c>
+      <c r="C15" t="s">
+        <v>201</v>
       </c>
       <c r="E15">
         <v>2018</v>
       </c>
       <c r="F15" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G15" t="s">
-        <v>149</v>
+        <v>202</v>
       </c>
       <c r="H15" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="I15" t="s">
         <v>25</v>
       </c>
       <c r="J15" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="K15" t="s">
         <v>28</v>
@@ -4375,7 +4420,7 @@
         <v>28</v>
       </c>
       <c r="Q15" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="R15" t="s">
         <v>28</v>
@@ -4386,37 +4431,31 @@
       <c r="U15" t="s">
         <v>42</v>
       </c>
-      <c r="X15" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W15" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>138812549</v>
+        <v>138812555</v>
       </c>
       <c r="B16" t="s">
-        <v>200</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>201</v>
+        <v>216</v>
+      </c>
+      <c r="C16" t="s">
+        <v>217</v>
       </c>
       <c r="E16">
-        <v>2018</v>
-      </c>
-      <c r="F16" t="s">
-        <v>205</v>
-      </c>
-      <c r="G16" t="s">
-        <v>202</v>
-      </c>
-      <c r="H16" t="s">
-        <v>203</v>
+        <v>2019</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J16" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="K16" t="s">
         <v>28</v>
@@ -4437,7 +4476,7 @@
         <v>28</v>
       </c>
       <c r="Q16" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="R16" t="s">
         <v>28</v>
@@ -4448,28 +4487,37 @@
       <c r="U16" t="s">
         <v>42</v>
       </c>
-      <c r="X16" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W16" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>138812555</v>
+        <v>138812556</v>
       </c>
       <c r="B17" t="s">
-        <v>216</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
+      </c>
+      <c r="C17" t="s">
+        <v>221</v>
       </c>
       <c r="E17">
-        <v>2019</v>
+        <v>2015</v>
+      </c>
+      <c r="F17" t="s">
+        <v>224</v>
+      </c>
+      <c r="G17" t="s">
+        <v>149</v>
+      </c>
+      <c r="H17" t="s">
+        <v>222</v>
       </c>
       <c r="I17" t="s">
         <v>114</v>
       </c>
       <c r="J17" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K17" t="s">
         <v>28</v>
@@ -4490,7 +4538,7 @@
         <v>28</v>
       </c>
       <c r="Q17" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="R17" t="s">
         <v>28</v>
@@ -4501,34 +4549,37 @@
       <c r="U17" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W17" t="s">
+        <v>852</v>
+      </c>
+      <c r="X17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>138812556</v>
+        <v>138812558</v>
       </c>
       <c r="B18" t="s">
-        <v>220</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>221</v>
+        <v>233</v>
+      </c>
+      <c r="C18" t="s">
+        <v>234</v>
       </c>
       <c r="E18">
-        <v>2015</v>
-      </c>
-      <c r="F18" t="s">
-        <v>224</v>
+        <v>2019</v>
       </c>
       <c r="G18" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="H18" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="I18" t="s">
         <v>114</v>
       </c>
       <c r="J18" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="K18" t="s">
         <v>28</v>
@@ -4549,7 +4600,7 @@
         <v>28</v>
       </c>
       <c r="Q18" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="R18" t="s">
         <v>28</v>
@@ -4561,33 +4612,36 @@
         <v>42</v>
       </c>
       <c r="W18" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+        <v>852</v>
+      </c>
+      <c r="X18" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>138812558</v>
+        <v>138812560</v>
       </c>
       <c r="B19" t="s">
-        <v>233</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
+      </c>
+      <c r="C19" t="s">
+        <v>241</v>
       </c>
       <c r="E19">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G19" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="H19" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I19" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J19" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="K19" t="s">
         <v>28</v>
@@ -4608,7 +4662,7 @@
         <v>28</v>
       </c>
       <c r="Q19" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="R19" t="s">
         <v>28</v>
@@ -4620,33 +4674,39 @@
         <v>42</v>
       </c>
       <c r="W19" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+        <v>852</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>138812560</v>
+        <v>138812581</v>
       </c>
       <c r="B20" t="s">
-        <v>240</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>241</v>
+        <v>260</v>
+      </c>
+      <c r="C20" t="s">
+        <v>261</v>
       </c>
       <c r="E20">
-        <v>2022</v>
+        <v>2020</v>
+      </c>
+      <c r="F20" t="s">
+        <v>265</v>
       </c>
       <c r="G20" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="H20" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="I20" t="s">
         <v>25</v>
       </c>
       <c r="J20" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="K20" t="s">
         <v>28</v>
@@ -4667,7 +4727,7 @@
         <v>28</v>
       </c>
       <c r="Q20" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="R20" t="s">
         <v>28</v>
@@ -4678,37 +4738,40 @@
       <c r="U20" t="s">
         <v>42</v>
       </c>
-      <c r="X20" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W20" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>138812581</v>
+        <v>138812594</v>
       </c>
       <c r="B21" t="s">
-        <v>260</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>261</v>
+        <v>268</v>
+      </c>
+      <c r="C21" t="s">
+        <v>269</v>
       </c>
       <c r="E21">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="F21" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="G21" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="H21" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="I21" t="s">
         <v>25</v>
       </c>
       <c r="J21" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="K21" t="s">
         <v>28</v>
@@ -4729,7 +4792,7 @@
         <v>28</v>
       </c>
       <c r="Q21" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="R21" t="s">
         <v>28</v>
@@ -4740,37 +4803,40 @@
       <c r="U21" t="s">
         <v>42</v>
       </c>
-      <c r="X21" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W21" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>138812594</v>
+        <v>138812651</v>
       </c>
       <c r="B22" t="s">
-        <v>268</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>269</v>
+        <v>290</v>
+      </c>
+      <c r="C22" t="s">
+        <v>291</v>
       </c>
       <c r="E22">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F22" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="G22" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="H22" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="I22" t="s">
         <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="K22" t="s">
         <v>28</v>
@@ -4791,7 +4857,7 @@
         <v>28</v>
       </c>
       <c r="Q22" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="R22" t="s">
         <v>28</v>
@@ -4802,37 +4868,37 @@
       <c r="U22" t="s">
         <v>42</v>
       </c>
-      <c r="X22" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W22" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>138812651</v>
+        <v>138812658</v>
       </c>
       <c r="B23" t="s">
-        <v>290</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>291</v>
+        <v>298</v>
+      </c>
+      <c r="C23" t="s">
+        <v>299</v>
       </c>
       <c r="E23">
-        <v>2021</v>
-      </c>
-      <c r="F23" t="s">
-        <v>295</v>
+        <v>2015</v>
       </c>
       <c r="G23" t="s">
-        <v>292</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="I23" t="s">
         <v>25</v>
       </c>
       <c r="J23" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="K23" t="s">
         <v>28</v>
@@ -4853,7 +4919,7 @@
         <v>28</v>
       </c>
       <c r="Q23" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="R23" t="s">
         <v>28</v>
@@ -4864,34 +4930,40 @@
       <c r="U23" t="s">
         <v>42</v>
       </c>
-      <c r="X23" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W23" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>138812658</v>
+        <v>138812754</v>
       </c>
       <c r="B24" t="s">
-        <v>298</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
+      </c>
+      <c r="C24" t="s">
+        <v>305</v>
       </c>
       <c r="E24">
-        <v>2015</v>
+        <v>2021</v>
+      </c>
+      <c r="F24" t="s">
+        <v>309</v>
       </c>
       <c r="G24" t="s">
-        <v>90</v>
+        <v>306</v>
       </c>
       <c r="H24" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="I24" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J24" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="K24" t="s">
         <v>28</v>
@@ -4912,7 +4984,7 @@
         <v>28</v>
       </c>
       <c r="Q24" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="R24" t="s">
         <v>28</v>
@@ -4923,37 +4995,37 @@
       <c r="U24" t="s">
         <v>42</v>
       </c>
+      <c r="W24" t="s">
+        <v>852</v>
+      </c>
       <c r="X24" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>138812754</v>
+        <v>138812905</v>
       </c>
       <c r="B25" t="s">
-        <v>304</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>305</v>
+        <v>334</v>
+      </c>
+      <c r="C25" t="s">
+        <v>335</v>
       </c>
       <c r="E25">
-        <v>2021</v>
-      </c>
-      <c r="F25" t="s">
-        <v>309</v>
+        <v>2022</v>
       </c>
       <c r="G25" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="H25" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="I25" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J25" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="K25" t="s">
         <v>28</v>
@@ -4974,7 +5046,7 @@
         <v>28</v>
       </c>
       <c r="Q25" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="R25" t="s">
         <v>28</v>
@@ -4986,36 +5058,39 @@
         <v>42</v>
       </c>
       <c r="W25" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+        <v>852</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>138812769</v>
+        <v>138812910</v>
       </c>
       <c r="B26" t="s">
-        <v>311</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>312</v>
+        <v>341</v>
+      </c>
+      <c r="C26" t="s">
+        <v>342</v>
       </c>
       <c r="E26">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F26" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="G26" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="H26" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="I26" t="s">
         <v>25</v>
       </c>
       <c r="J26" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="K26" t="s">
         <v>28</v>
@@ -5036,7 +5111,7 @@
         <v>28</v>
       </c>
       <c r="Q26" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="R26" t="s">
         <v>28</v>
@@ -5047,34 +5122,40 @@
       <c r="U26" t="s">
         <v>42</v>
       </c>
-      <c r="X26" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W26" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>138812905</v>
+        <v>138812965</v>
       </c>
       <c r="B27" t="s">
-        <v>334</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>335</v>
+        <v>349</v>
+      </c>
+      <c r="C27" t="s">
+        <v>350</v>
       </c>
       <c r="E27">
-        <v>2022</v>
+        <v>2021</v>
+      </c>
+      <c r="F27" t="s">
+        <v>353</v>
       </c>
       <c r="G27" t="s">
-        <v>336</v>
+        <v>128</v>
       </c>
       <c r="H27" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="I27" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J27" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="K27" t="s">
         <v>28</v>
@@ -5095,7 +5176,7 @@
         <v>28</v>
       </c>
       <c r="Q27" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="R27" t="s">
         <v>28</v>
@@ -5106,37 +5187,40 @@
       <c r="U27" t="s">
         <v>42</v>
       </c>
+      <c r="W27" t="s">
+        <v>852</v>
+      </c>
       <c r="X27" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>138812910</v>
+        <v>138813011</v>
       </c>
       <c r="B28" t="s">
-        <v>341</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>342</v>
+        <v>377</v>
+      </c>
+      <c r="C28" t="s">
+        <v>378</v>
       </c>
       <c r="E28">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F28" t="s">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="G28" t="s">
-        <v>343</v>
+        <v>379</v>
       </c>
       <c r="H28" t="s">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="I28" t="s">
         <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>345</v>
+        <v>381</v>
       </c>
       <c r="K28" t="s">
         <v>28</v>
@@ -5157,7 +5241,7 @@
         <v>28</v>
       </c>
       <c r="Q28" t="s">
-        <v>347</v>
+        <v>383</v>
       </c>
       <c r="R28" t="s">
         <v>28</v>
@@ -5168,37 +5252,40 @@
       <c r="U28" t="s">
         <v>42</v>
       </c>
-      <c r="X28" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W28" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>138812965</v>
+        <v>138813062</v>
       </c>
       <c r="B29" t="s">
-        <v>349</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>350</v>
+        <v>413</v>
+      </c>
+      <c r="C29" t="s">
+        <v>414</v>
       </c>
       <c r="E29">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="F29" t="s">
-        <v>353</v>
+        <v>418</v>
       </c>
       <c r="G29" t="s">
-        <v>128</v>
+        <v>415</v>
       </c>
       <c r="H29" t="s">
-        <v>351</v>
+        <v>416</v>
       </c>
       <c r="I29" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>352</v>
+        <v>417</v>
       </c>
       <c r="K29" t="s">
         <v>28</v>
@@ -5219,7 +5306,7 @@
         <v>28</v>
       </c>
       <c r="Q29" t="s">
-        <v>354</v>
+        <v>419</v>
       </c>
       <c r="R29" t="s">
         <v>28</v>
@@ -5231,36 +5318,36 @@
         <v>42</v>
       </c>
       <c r="W29" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+        <v>852</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>138813002</v>
+        <v>138813195</v>
       </c>
       <c r="B30" t="s">
-        <v>371</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>372</v>
+        <v>463</v>
+      </c>
+      <c r="C30" t="s">
+        <v>464</v>
       </c>
       <c r="E30">
-        <v>2021</v>
-      </c>
-      <c r="F30" t="s">
-        <v>375</v>
+        <v>2016</v>
       </c>
       <c r="G30" t="s">
-        <v>149</v>
+        <v>358</v>
       </c>
       <c r="H30" t="s">
-        <v>373</v>
+        <v>465</v>
       </c>
       <c r="I30" t="s">
         <v>25</v>
       </c>
       <c r="J30" t="s">
-        <v>374</v>
+        <v>466</v>
       </c>
       <c r="K30" t="s">
         <v>28</v>
@@ -5281,54 +5368,51 @@
         <v>28</v>
       </c>
       <c r="Q30" t="s">
-        <v>376</v>
+        <v>467</v>
       </c>
       <c r="R30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="S30" t="s">
-        <v>33</v>
-      </c>
-      <c r="T30" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="U30" t="s">
-        <v>836</v>
-      </c>
-      <c r="V30" t="s">
-        <v>842</v>
-      </c>
-      <c r="X30" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="W30" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>138813011</v>
+        <v>138813221</v>
       </c>
       <c r="B31" t="s">
-        <v>377</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>378</v>
+        <v>469</v>
+      </c>
+      <c r="C31" t="s">
+        <v>470</v>
       </c>
       <c r="E31">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="F31" t="s">
-        <v>382</v>
+        <v>474</v>
       </c>
       <c r="G31" t="s">
-        <v>379</v>
+        <v>471</v>
       </c>
       <c r="H31" t="s">
-        <v>380</v>
+        <v>472</v>
       </c>
       <c r="I31" t="s">
         <v>25</v>
       </c>
       <c r="J31" t="s">
-        <v>381</v>
+        <v>473</v>
       </c>
       <c r="K31" t="s">
         <v>28</v>
@@ -5349,7 +5433,7 @@
         <v>28</v>
       </c>
       <c r="Q31" t="s">
-        <v>383</v>
+        <v>475</v>
       </c>
       <c r="R31" t="s">
         <v>28</v>
@@ -5360,37 +5444,40 @@
       <c r="U31" t="s">
         <v>42</v>
       </c>
-      <c r="X31" t="s">
+      <c r="W31" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y31" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>138813037</v>
+        <v>138813294</v>
       </c>
       <c r="B32" t="s">
-        <v>384</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>385</v>
+        <v>489</v>
+      </c>
+      <c r="C32" t="s">
+        <v>490</v>
       </c>
       <c r="E32">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F32" t="s">
-        <v>389</v>
+        <v>494</v>
       </c>
       <c r="G32" t="s">
-        <v>386</v>
+        <v>491</v>
       </c>
       <c r="H32" t="s">
-        <v>387</v>
+        <v>492</v>
       </c>
       <c r="I32" t="s">
         <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>388</v>
+        <v>493</v>
       </c>
       <c r="K32" t="s">
         <v>28</v>
@@ -5411,54 +5498,51 @@
         <v>28</v>
       </c>
       <c r="Q32" t="s">
-        <v>390</v>
+        <v>495</v>
       </c>
       <c r="R32" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="S32" t="s">
-        <v>33</v>
-      </c>
-      <c r="T32" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="U32" t="s">
-        <v>836</v>
-      </c>
-      <c r="V32" t="s">
-        <v>838</v>
-      </c>
-      <c r="X32" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="W32" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>138813062</v>
+        <v>138813388</v>
       </c>
       <c r="B33" t="s">
-        <v>413</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>414</v>
+        <v>497</v>
+      </c>
+      <c r="C33" t="s">
+        <v>498</v>
       </c>
       <c r="E33">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="F33" t="s">
-        <v>418</v>
+        <v>502</v>
       </c>
       <c r="G33" t="s">
-        <v>415</v>
+        <v>499</v>
       </c>
       <c r="H33" t="s">
-        <v>416</v>
+        <v>500</v>
       </c>
       <c r="I33" t="s">
         <v>25</v>
       </c>
       <c r="J33" t="s">
-        <v>417</v>
+        <v>501</v>
       </c>
       <c r="K33" t="s">
         <v>28</v>
@@ -5479,7 +5563,7 @@
         <v>28</v>
       </c>
       <c r="Q33" t="s">
-        <v>419</v>
+        <v>503</v>
       </c>
       <c r="R33" t="s">
         <v>28</v>
@@ -5490,34 +5574,40 @@
       <c r="U33" t="s">
         <v>42</v>
       </c>
-      <c r="X33" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W33" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>138813195</v>
+        <v>138813415</v>
       </c>
       <c r="B34" t="s">
-        <v>463</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>464</v>
+        <v>511</v>
+      </c>
+      <c r="C34" t="s">
+        <v>512</v>
       </c>
       <c r="E34">
-        <v>2016</v>
+        <v>2017</v>
+      </c>
+      <c r="F34" t="s">
+        <v>516</v>
       </c>
       <c r="G34" t="s">
-        <v>358</v>
+        <v>513</v>
       </c>
       <c r="H34" t="s">
-        <v>465</v>
+        <v>514</v>
       </c>
       <c r="I34" t="s">
         <v>25</v>
       </c>
       <c r="J34" t="s">
-        <v>466</v>
+        <v>515</v>
       </c>
       <c r="K34" t="s">
         <v>28</v>
@@ -5538,7 +5628,7 @@
         <v>28</v>
       </c>
       <c r="Q34" t="s">
-        <v>467</v>
+        <v>517</v>
       </c>
       <c r="R34" t="s">
         <v>28</v>
@@ -5549,37 +5639,40 @@
       <c r="U34" t="s">
         <v>42</v>
       </c>
-      <c r="X34" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W34" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>138813221</v>
+        <v>138813597</v>
       </c>
       <c r="B35" t="s">
-        <v>469</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>470</v>
+        <v>536</v>
+      </c>
+      <c r="C35" t="s">
+        <v>537</v>
       </c>
       <c r="E35">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="F35" t="s">
-        <v>474</v>
+        <v>541</v>
       </c>
       <c r="G35" t="s">
-        <v>471</v>
+        <v>538</v>
       </c>
       <c r="H35" t="s">
-        <v>472</v>
+        <v>539</v>
       </c>
       <c r="I35" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J35" t="s">
-        <v>473</v>
+        <v>540</v>
       </c>
       <c r="K35" t="s">
         <v>28</v>
@@ -5600,7 +5693,7 @@
         <v>28</v>
       </c>
       <c r="Q35" t="s">
-        <v>475</v>
+        <v>542</v>
       </c>
       <c r="R35" t="s">
         <v>28</v>
@@ -5611,37 +5704,40 @@
       <c r="U35" t="s">
         <v>42</v>
       </c>
+      <c r="W35" t="s">
+        <v>852</v>
+      </c>
       <c r="X35" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>138813294</v>
+        <v>138813606</v>
       </c>
       <c r="B36" t="s">
-        <v>489</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>490</v>
+        <v>544</v>
+      </c>
+      <c r="C36" t="s">
+        <v>545</v>
       </c>
       <c r="E36">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="F36" t="s">
-        <v>494</v>
+        <v>549</v>
       </c>
       <c r="G36" t="s">
-        <v>491</v>
+        <v>546</v>
       </c>
       <c r="H36" t="s">
-        <v>492</v>
+        <v>547</v>
       </c>
       <c r="I36" t="s">
         <v>25</v>
       </c>
       <c r="J36" t="s">
-        <v>493</v>
+        <v>548</v>
       </c>
       <c r="K36" t="s">
         <v>28</v>
@@ -5662,7 +5758,7 @@
         <v>28</v>
       </c>
       <c r="Q36" t="s">
-        <v>495</v>
+        <v>58</v>
       </c>
       <c r="R36" t="s">
         <v>28</v>
@@ -5673,37 +5769,40 @@
       <c r="U36" t="s">
         <v>42</v>
       </c>
-      <c r="X36" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W36" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>138813388</v>
+        <v>138813651</v>
       </c>
       <c r="B37" t="s">
-        <v>497</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>498</v>
+        <v>551</v>
+      </c>
+      <c r="C37" t="s">
+        <v>552</v>
       </c>
       <c r="E37">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="F37" t="s">
-        <v>502</v>
+        <v>556</v>
       </c>
       <c r="G37" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="H37" t="s">
-        <v>500</v>
+        <v>554</v>
       </c>
       <c r="I37" t="s">
         <v>25</v>
       </c>
       <c r="J37" t="s">
-        <v>501</v>
+        <v>555</v>
       </c>
       <c r="K37" t="s">
         <v>28</v>
@@ -5720,11 +5819,8 @@
       <c r="O37" t="s">
         <v>28</v>
       </c>
-      <c r="P37" t="s">
-        <v>28</v>
-      </c>
       <c r="Q37" t="s">
-        <v>503</v>
+        <v>557</v>
       </c>
       <c r="R37" t="s">
         <v>28</v>
@@ -5735,37 +5831,34 @@
       <c r="U37" t="s">
         <v>42</v>
       </c>
-      <c r="X37" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W37" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>138813415</v>
+        <v>138814066</v>
       </c>
       <c r="B38" t="s">
-        <v>511</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>512</v>
+        <v>566</v>
+      </c>
+      <c r="C38" t="s">
+        <v>567</v>
       </c>
       <c r="E38">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="F38" t="s">
-        <v>516</v>
-      </c>
-      <c r="G38" t="s">
-        <v>513</v>
-      </c>
-      <c r="H38" t="s">
-        <v>514</v>
+        <v>569</v>
       </c>
       <c r="I38" t="s">
         <v>25</v>
       </c>
       <c r="J38" t="s">
-        <v>515</v>
+        <v>568</v>
       </c>
       <c r="K38" t="s">
         <v>28</v>
@@ -5786,7 +5879,7 @@
         <v>28</v>
       </c>
       <c r="Q38" t="s">
-        <v>517</v>
+        <v>570</v>
       </c>
       <c r="R38" t="s">
         <v>28</v>
@@ -5797,158 +5890,167 @@
       <c r="U38" t="s">
         <v>42</v>
       </c>
-      <c r="X38" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W38" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>138813419</v>
+        <v>138814577</v>
       </c>
       <c r="B39" t="s">
-        <v>839</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>840</v>
+        <v>574</v>
+      </c>
+      <c r="C39" t="s">
+        <v>575</v>
       </c>
       <c r="E39">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="F39" t="s">
-        <v>841</v>
+        <v>578</v>
+      </c>
+      <c r="G39" t="s">
+        <v>149</v>
+      </c>
+      <c r="H39" t="s">
+        <v>576</v>
       </c>
       <c r="I39" t="s">
-        <v>812</v>
+        <v>25</v>
       </c>
       <c r="J39" t="s">
-        <v>812</v>
+        <v>577</v>
       </c>
       <c r="K39" t="s">
-        <v>812</v>
+        <v>28</v>
       </c>
       <c r="L39" t="s">
-        <v>812</v>
+        <v>30</v>
       </c>
       <c r="M39" t="s">
-        <v>812</v>
+        <v>28</v>
       </c>
       <c r="N39" t="s">
-        <v>812</v>
+        <v>28</v>
       </c>
       <c r="O39" t="s">
-        <v>812</v>
+        <v>28</v>
       </c>
       <c r="P39" t="s">
-        <v>812</v>
+        <v>28</v>
       </c>
       <c r="Q39" t="s">
-        <v>812</v>
+        <v>579</v>
       </c>
       <c r="R39" t="s">
-        <v>812</v>
+        <v>28</v>
       </c>
       <c r="S39" t="s">
-        <v>812</v>
+        <v>42</v>
       </c>
       <c r="U39" t="s">
-        <v>836</v>
-      </c>
-      <c r="V39" t="s">
-        <v>838</v>
-      </c>
-      <c r="X39" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="W39" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>138813552</v>
+        <v>138814765</v>
       </c>
       <c r="B40" t="s">
-        <v>533</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>534</v>
+        <v>600</v>
+      </c>
+      <c r="C40" t="s">
+        <v>601</v>
       </c>
       <c r="E40">
-        <v>2011</v>
+        <v>2024</v>
+      </c>
+      <c r="F40" t="s">
+        <v>605</v>
+      </c>
+      <c r="G40" t="s">
+        <v>602</v>
+      </c>
+      <c r="H40" t="s">
+        <v>603</v>
       </c>
       <c r="I40" t="s">
+        <v>114</v>
+      </c>
+      <c r="J40" t="s">
+        <v>604</v>
+      </c>
+      <c r="K40" t="s">
+        <v>28</v>
+      </c>
+      <c r="L40" t="s">
+        <v>30</v>
+      </c>
+      <c r="M40" t="s">
+        <v>28</v>
+      </c>
+      <c r="N40" t="s">
+        <v>28</v>
+      </c>
+      <c r="O40" t="s">
+        <v>28</v>
+      </c>
+      <c r="P40" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>606</v>
+      </c>
+      <c r="R40" t="s">
+        <v>28</v>
+      </c>
+      <c r="S40" t="s">
+        <v>42</v>
+      </c>
+      <c r="U40" t="s">
+        <v>42</v>
+      </c>
+      <c r="W40" t="s">
+        <v>852</v>
+      </c>
+      <c r="X40" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>138814830</v>
+      </c>
+      <c r="B41" t="s">
+        <v>614</v>
+      </c>
+      <c r="C41" t="s">
+        <v>615</v>
+      </c>
+      <c r="E41">
+        <v>2003</v>
+      </c>
+      <c r="F41" t="s">
+        <v>617</v>
+      </c>
+      <c r="G41" t="s">
+        <v>187</v>
+      </c>
+      <c r="I41" t="s">
         <v>25</v>
       </c>
-      <c r="J40" t="s">
-        <v>535</v>
-      </c>
-      <c r="K40" t="s">
-        <v>28</v>
-      </c>
-      <c r="L40" t="s">
-        <v>30</v>
-      </c>
-      <c r="M40" t="s">
-        <v>28</v>
-      </c>
-      <c r="N40" t="s">
-        <v>28</v>
-      </c>
-      <c r="O40" t="s">
-        <v>28</v>
-      </c>
-      <c r="P40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>531</v>
-      </c>
-      <c r="R40" t="s">
-        <v>28</v>
-      </c>
-      <c r="S40" t="s">
-        <v>33</v>
-      </c>
-      <c r="T40" t="s">
-        <v>522</v>
-      </c>
-      <c r="U40" t="s">
-        <v>836</v>
-      </c>
-      <c r="V40" t="s">
-        <v>811</v>
-      </c>
-      <c r="W40" t="s">
-        <v>523</v>
-      </c>
-      <c r="X40" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>138813597</v>
-      </c>
-      <c r="B41" t="s">
-        <v>536</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="E41">
-        <v>2021</v>
-      </c>
-      <c r="F41" t="s">
-        <v>541</v>
-      </c>
-      <c r="G41" t="s">
-        <v>538</v>
-      </c>
-      <c r="H41" t="s">
-        <v>539</v>
-      </c>
-      <c r="I41" t="s">
-        <v>114</v>
-      </c>
       <c r="J41" t="s">
-        <v>540</v>
+        <v>616</v>
       </c>
       <c r="K41" t="s">
         <v>28</v>
@@ -5969,7 +6071,7 @@
         <v>28</v>
       </c>
       <c r="Q41" t="s">
-        <v>542</v>
+        <v>618</v>
       </c>
       <c r="R41" t="s">
         <v>28</v>
@@ -5981,36 +6083,36 @@
         <v>42</v>
       </c>
       <c r="W41" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+        <v>852</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>138813606</v>
+        <v>138814856</v>
       </c>
       <c r="B42" t="s">
-        <v>544</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>545</v>
+        <v>620</v>
+      </c>
+      <c r="C42" t="s">
+        <v>621</v>
       </c>
       <c r="E42">
-        <v>2017</v>
-      </c>
-      <c r="F42" t="s">
-        <v>549</v>
+        <v>2023</v>
       </c>
       <c r="G42" t="s">
-        <v>546</v>
+        <v>622</v>
       </c>
       <c r="H42" t="s">
-        <v>547</v>
+        <v>623</v>
       </c>
       <c r="I42" t="s">
         <v>25</v>
       </c>
       <c r="J42" t="s">
-        <v>548</v>
+        <v>624</v>
       </c>
       <c r="K42" t="s">
         <v>28</v>
@@ -6031,7 +6133,7 @@
         <v>28</v>
       </c>
       <c r="Q42" t="s">
-        <v>58</v>
+        <v>625</v>
       </c>
       <c r="R42" t="s">
         <v>28</v>
@@ -6042,37 +6144,40 @@
       <c r="U42" t="s">
         <v>42</v>
       </c>
-      <c r="X42" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W42" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>138813651</v>
+        <v>138816736</v>
       </c>
       <c r="B43" t="s">
-        <v>551</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>552</v>
+        <v>638</v>
+      </c>
+      <c r="C43" t="s">
+        <v>639</v>
       </c>
       <c r="E43">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="F43" t="s">
-        <v>556</v>
+        <v>642</v>
       </c>
       <c r="G43" t="s">
-        <v>553</v>
+        <v>407</v>
       </c>
       <c r="H43" t="s">
-        <v>554</v>
+        <v>640</v>
       </c>
       <c r="I43" t="s">
         <v>25</v>
       </c>
       <c r="J43" t="s">
-        <v>555</v>
+        <v>641</v>
       </c>
       <c r="K43" t="s">
         <v>28</v>
@@ -6089,8 +6194,11 @@
       <c r="O43" t="s">
         <v>28</v>
       </c>
+      <c r="P43" t="s">
+        <v>28</v>
+      </c>
       <c r="Q43" t="s">
-        <v>557</v>
+        <v>643</v>
       </c>
       <c r="R43" t="s">
         <v>28</v>
@@ -6101,31 +6209,31 @@
       <c r="U43" t="s">
         <v>42</v>
       </c>
-      <c r="X43" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W43" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>138814066</v>
+        <v>138816901</v>
       </c>
       <c r="B44" t="s">
-        <v>566</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>567</v>
+        <v>644</v>
+      </c>
+      <c r="C44" t="s">
+        <v>645</v>
       </c>
       <c r="E44">
-        <v>2013</v>
-      </c>
-      <c r="F44" t="s">
-        <v>569</v>
+        <v>2022</v>
       </c>
       <c r="I44" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J44" t="s">
-        <v>568</v>
+        <v>646</v>
       </c>
       <c r="K44" t="s">
         <v>28</v>
@@ -6146,7 +6254,7 @@
         <v>28</v>
       </c>
       <c r="Q44" t="s">
-        <v>570</v>
+        <v>647</v>
       </c>
       <c r="R44" t="s">
         <v>28</v>
@@ -6157,34 +6265,31 @@
       <c r="U44" t="s">
         <v>42</v>
       </c>
+      <c r="W44" t="s">
+        <v>852</v>
+      </c>
       <c r="X44" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>138814502</v>
+        <v>138816982</v>
       </c>
       <c r="B45" t="s">
-        <v>572</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>848</v>
+        <v>658</v>
+      </c>
+      <c r="C45" t="s">
+        <v>659</v>
       </c>
       <c r="E45">
-        <v>2013</v>
-      </c>
-      <c r="G45" t="s">
-        <v>90</v>
-      </c>
-      <c r="H45" t="s">
-        <v>849</v>
+        <v>2010</v>
       </c>
       <c r="I45" t="s">
         <v>25</v>
       </c>
       <c r="J45" t="s">
-        <v>573</v>
+        <v>660</v>
       </c>
       <c r="K45" t="s">
         <v>28</v>
@@ -6204,52 +6309,52 @@
       <c r="P45" t="s">
         <v>28</v>
       </c>
+      <c r="Q45" t="s">
+        <v>661</v>
+      </c>
       <c r="R45" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="S45" t="s">
-        <v>33</v>
-      </c>
-      <c r="T45" t="s">
-        <v>455</v>
+        <v>42</v>
       </c>
       <c r="U45" t="s">
-        <v>836</v>
-      </c>
-      <c r="V45" t="s">
-        <v>838</v>
-      </c>
-      <c r="X45" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="W45" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>138814577</v>
+        <v>153488790</v>
       </c>
       <c r="B46" t="s">
-        <v>574</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>575</v>
+        <v>725</v>
+      </c>
+      <c r="C46" t="s">
+        <v>726</v>
       </c>
       <c r="E46">
-        <v>2008</v>
+        <v>1990</v>
       </c>
       <c r="F46" t="s">
-        <v>578</v>
+        <v>722</v>
       </c>
       <c r="G46" t="s">
-        <v>149</v>
+        <v>715</v>
       </c>
       <c r="H46" t="s">
-        <v>576</v>
+        <v>715</v>
       </c>
       <c r="I46" t="s">
         <v>25</v>
       </c>
       <c r="J46" t="s">
-        <v>577</v>
+        <v>727</v>
       </c>
       <c r="K46" t="s">
         <v>28</v>
@@ -6270,7 +6375,7 @@
         <v>28</v>
       </c>
       <c r="Q46" t="s">
-        <v>579</v>
+        <v>728</v>
       </c>
       <c r="R46" t="s">
         <v>28</v>
@@ -6281,34 +6386,40 @@
       <c r="U46" t="s">
         <v>42</v>
       </c>
-      <c r="X46" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W46" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>138814734</v>
+        <v>153489230</v>
       </c>
       <c r="B47" t="s">
-        <v>594</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>595</v>
+        <v>765</v>
+      </c>
+      <c r="C47" t="s">
+        <v>766</v>
       </c>
       <c r="E47">
-        <v>2024</v>
+        <v>2011</v>
+      </c>
+      <c r="F47" t="s">
+        <v>770</v>
       </c>
       <c r="G47" t="s">
-        <v>596</v>
+        <v>767</v>
       </c>
       <c r="H47" t="s">
-        <v>597</v>
+        <v>768</v>
       </c>
       <c r="I47" t="s">
         <v>25</v>
       </c>
       <c r="J47" t="s">
-        <v>598</v>
+        <v>769</v>
       </c>
       <c r="K47" t="s">
         <v>28</v>
@@ -6329,7 +6440,7 @@
         <v>28</v>
       </c>
       <c r="Q47" t="s">
-        <v>599</v>
+        <v>771</v>
       </c>
       <c r="R47" t="s">
         <v>28</v>
@@ -6340,96 +6451,111 @@
       <c r="U47" t="s">
         <v>42</v>
       </c>
-      <c r="X47" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>138814765</v>
+      <c r="W47" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>806</v>
       </c>
       <c r="B48" t="s">
-        <v>600</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>601</v>
+        <v>812</v>
+      </c>
+      <c r="C48" t="s">
+        <v>813</v>
+      </c>
+      <c r="D48" t="s">
+        <v>812</v>
       </c>
       <c r="E48">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="F48" t="s">
-        <v>605</v>
+        <v>812</v>
       </c>
       <c r="G48" t="s">
-        <v>602</v>
+        <v>812</v>
       </c>
       <c r="H48" t="s">
-        <v>603</v>
+        <v>815</v>
       </c>
       <c r="I48" t="s">
-        <v>114</v>
+        <v>812</v>
       </c>
       <c r="J48" t="s">
-        <v>604</v>
+        <v>812</v>
       </c>
       <c r="K48" t="s">
-        <v>28</v>
+        <v>812</v>
       </c>
       <c r="L48" t="s">
-        <v>30</v>
+        <v>812</v>
       </c>
       <c r="M48" t="s">
-        <v>28</v>
+        <v>812</v>
       </c>
       <c r="N48" t="s">
-        <v>28</v>
+        <v>812</v>
       </c>
       <c r="O48" t="s">
-        <v>28</v>
+        <v>812</v>
       </c>
       <c r="P48" t="s">
-        <v>28</v>
+        <v>812</v>
       </c>
       <c r="Q48" t="s">
-        <v>606</v>
+        <v>812</v>
       </c>
       <c r="R48" t="s">
-        <v>28</v>
+        <v>812</v>
       </c>
       <c r="S48" t="s">
-        <v>42</v>
+        <v>812</v>
+      </c>
+      <c r="T48" t="s">
+        <v>812</v>
       </c>
       <c r="U48" t="s">
         <v>42</v>
       </c>
+      <c r="V48" t="s">
+        <v>819</v>
+      </c>
       <c r="W48" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>138814830</v>
+        <v>138813002</v>
       </c>
       <c r="B49" t="s">
-        <v>614</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>615</v>
+        <v>371</v>
+      </c>
+      <c r="C49" t="s">
+        <v>372</v>
       </c>
       <c r="E49">
-        <v>2003</v>
+        <v>2021</v>
       </c>
       <c r="F49" t="s">
-        <v>617</v>
+        <v>375</v>
       </c>
       <c r="G49" t="s">
-        <v>187</v>
+        <v>149</v>
+      </c>
+      <c r="H49" t="s">
+        <v>373</v>
       </c>
       <c r="I49" t="s">
         <v>25</v>
       </c>
       <c r="J49" t="s">
-        <v>616</v>
+        <v>374</v>
       </c>
       <c r="K49" t="s">
         <v>28</v>
@@ -6450,45 +6576,57 @@
         <v>28</v>
       </c>
       <c r="Q49" t="s">
-        <v>618</v>
+        <v>376</v>
       </c>
       <c r="R49" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="S49" t="s">
-        <v>42</v>
+        <v>33</v>
+      </c>
+      <c r="T49" t="s">
+        <v>27</v>
       </c>
       <c r="U49" t="s">
-        <v>42</v>
-      </c>
-      <c r="X49" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+        <v>836</v>
+      </c>
+      <c r="V49" t="s">
+        <v>842</v>
+      </c>
+      <c r="W49" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>138814856</v>
+        <v>138813037</v>
       </c>
       <c r="B50" t="s">
-        <v>620</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>621</v>
+        <v>384</v>
+      </c>
+      <c r="C50" t="s">
+        <v>385</v>
       </c>
       <c r="E50">
-        <v>2023</v>
+        <v>2016</v>
+      </c>
+      <c r="F50" t="s">
+        <v>389</v>
       </c>
       <c r="G50" t="s">
-        <v>622</v>
+        <v>386</v>
       </c>
       <c r="H50" t="s">
-        <v>623</v>
+        <v>387</v>
       </c>
       <c r="I50" t="s">
         <v>25</v>
       </c>
       <c r="J50" t="s">
-        <v>624</v>
+        <v>388</v>
       </c>
       <c r="K50" t="s">
         <v>28</v>
@@ -6509,101 +6647,110 @@
         <v>28</v>
       </c>
       <c r="Q50" t="s">
-        <v>625</v>
+        <v>390</v>
       </c>
       <c r="R50" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="S50" t="s">
-        <v>42</v>
+        <v>33</v>
+      </c>
+      <c r="T50" t="s">
+        <v>27</v>
       </c>
       <c r="U50" t="s">
-        <v>42</v>
-      </c>
-      <c r="X50" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+        <v>836</v>
+      </c>
+      <c r="V50" t="s">
+        <v>838</v>
+      </c>
+      <c r="W50" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>138816059</v>
+        <v>138813419</v>
       </c>
       <c r="B51" t="s">
-        <v>633</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>634</v>
+        <v>839</v>
+      </c>
+      <c r="C51" t="s">
+        <v>840</v>
       </c>
       <c r="E51">
-        <v>2018</v>
+        <v>2017</v>
+      </c>
+      <c r="F51" t="s">
+        <v>841</v>
       </c>
       <c r="I51" t="s">
-        <v>25</v>
+        <v>812</v>
       </c>
       <c r="J51" t="s">
-        <v>635</v>
+        <v>812</v>
       </c>
       <c r="K51" t="s">
-        <v>28</v>
+        <v>812</v>
       </c>
       <c r="L51" t="s">
-        <v>30</v>
+        <v>812</v>
       </c>
       <c r="M51" t="s">
-        <v>28</v>
+        <v>812</v>
       </c>
       <c r="N51" t="s">
-        <v>28</v>
+        <v>812</v>
       </c>
       <c r="O51" t="s">
-        <v>28</v>
+        <v>812</v>
       </c>
       <c r="P51" t="s">
-        <v>28</v>
+        <v>812</v>
       </c>
       <c r="Q51" t="s">
-        <v>636</v>
+        <v>812</v>
       </c>
       <c r="R51" t="s">
-        <v>28</v>
+        <v>812</v>
       </c>
       <c r="S51" t="s">
-        <v>42</v>
+        <v>812</v>
       </c>
       <c r="U51" t="s">
-        <v>42</v>
-      </c>
-      <c r="X51" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+        <v>836</v>
+      </c>
+      <c r="V51" t="s">
+        <v>838</v>
+      </c>
+      <c r="W51" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>138816736</v>
+        <v>138813552</v>
       </c>
       <c r="B52" t="s">
-        <v>638</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>639</v>
+        <v>533</v>
+      </c>
+      <c r="C52" t="s">
+        <v>534</v>
       </c>
       <c r="E52">
         <v>2011</v>
       </c>
-      <c r="F52" t="s">
-        <v>642</v>
-      </c>
-      <c r="G52" t="s">
-        <v>407</v>
-      </c>
-      <c r="H52" t="s">
-        <v>640</v>
-      </c>
       <c r="I52" t="s">
         <v>25</v>
       </c>
       <c r="J52" t="s">
-        <v>641</v>
+        <v>535</v>
       </c>
       <c r="K52" t="s">
         <v>28</v>
@@ -6624,39 +6771,57 @@
         <v>28</v>
       </c>
       <c r="Q52" t="s">
-        <v>643</v>
+        <v>531</v>
       </c>
       <c r="R52" t="s">
         <v>28</v>
       </c>
       <c r="S52" t="s">
-        <v>42</v>
+        <v>33</v>
+      </c>
+      <c r="T52" t="s">
+        <v>522</v>
       </c>
       <c r="U52" t="s">
-        <v>42</v>
+        <v>836</v>
+      </c>
+      <c r="V52" t="s">
+        <v>811</v>
+      </c>
+      <c r="W52" t="s">
+        <v>852</v>
       </c>
       <c r="X52" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+        <v>523</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>138816901</v>
+        <v>138814502</v>
       </c>
       <c r="B53" t="s">
-        <v>644</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>645</v>
+        <v>572</v>
+      </c>
+      <c r="C53" t="s">
+        <v>848</v>
       </c>
       <c r="E53">
-        <v>2022</v>
+        <v>2013</v>
+      </c>
+      <c r="G53" t="s">
+        <v>90</v>
+      </c>
+      <c r="H53" t="s">
+        <v>849</v>
       </c>
       <c r="I53" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J53" t="s">
-        <v>646</v>
+        <v>573</v>
       </c>
       <c r="K53" t="s">
         <v>28</v>
@@ -6676,40 +6841,55 @@
       <c r="P53" t="s">
         <v>28</v>
       </c>
-      <c r="Q53" t="s">
-        <v>647</v>
-      </c>
       <c r="R53" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="S53" t="s">
-        <v>42</v>
+        <v>33</v>
+      </c>
+      <c r="T53" t="s">
+        <v>455</v>
       </c>
       <c r="U53" t="s">
-        <v>42</v>
+        <v>836</v>
+      </c>
+      <c r="V53" t="s">
+        <v>838</v>
       </c>
       <c r="W53" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+        <v>852</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>138816982</v>
+        <v>174015352</v>
       </c>
       <c r="B54" t="s">
-        <v>658</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>659</v>
+        <v>773</v>
+      </c>
+      <c r="C54" t="s">
+        <v>774</v>
+      </c>
+      <c r="D54" t="s">
+        <v>775</v>
       </c>
       <c r="E54">
-        <v>2010</v>
+        <v>2012</v>
+      </c>
+      <c r="F54" t="s">
+        <v>777</v>
+      </c>
+      <c r="H54" t="s">
+        <v>507</v>
       </c>
       <c r="I54" t="s">
         <v>25</v>
       </c>
       <c r="J54" t="s">
-        <v>660</v>
+        <v>776</v>
       </c>
       <c r="K54" t="s">
         <v>28</v>
@@ -6730,48 +6910,60 @@
         <v>28</v>
       </c>
       <c r="Q54" t="s">
-        <v>661</v>
+        <v>618</v>
       </c>
       <c r="R54" t="s">
         <v>28</v>
       </c>
       <c r="S54" t="s">
-        <v>42</v>
+        <v>33</v>
+      </c>
+      <c r="T54" t="s">
+        <v>522</v>
       </c>
       <c r="U54" t="s">
-        <v>42</v>
+        <v>836</v>
+      </c>
+      <c r="V54" t="s">
+        <v>837</v>
+      </c>
+      <c r="W54" t="s">
+        <v>852</v>
       </c>
       <c r="X54" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+        <v>523</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>153488790</v>
+        <v>138812769</v>
       </c>
       <c r="B55" t="s">
-        <v>725</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>726</v>
+        <v>311</v>
+      </c>
+      <c r="C55" t="s">
+        <v>312</v>
       </c>
       <c r="E55">
-        <v>1990</v>
+        <v>2022</v>
       </c>
       <c r="F55" t="s">
-        <v>722</v>
+        <v>316</v>
       </c>
       <c r="G55" t="s">
-        <v>715</v>
+        <v>313</v>
       </c>
       <c r="H55" t="s">
-        <v>715</v>
+        <v>314</v>
       </c>
       <c r="I55" t="s">
         <v>25</v>
       </c>
       <c r="J55" t="s">
-        <v>727</v>
+        <v>315</v>
       </c>
       <c r="K55" t="s">
         <v>28</v>
@@ -6792,7 +6984,7 @@
         <v>28</v>
       </c>
       <c r="Q55" t="s">
-        <v>728</v>
+        <v>317</v>
       </c>
       <c r="R55" t="s">
         <v>28</v>
@@ -6803,37 +6995,37 @@
       <c r="U55" t="s">
         <v>42</v>
       </c>
-      <c r="X55" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W55" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>153488800</v>
+        <v>138814734</v>
       </c>
       <c r="B56" t="s">
-        <v>729</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>730</v>
+        <v>594</v>
+      </c>
+      <c r="C56" t="s">
+        <v>595</v>
       </c>
       <c r="E56">
-        <v>1999</v>
-      </c>
-      <c r="F56" t="s">
-        <v>722</v>
+        <v>2024</v>
       </c>
       <c r="G56" t="s">
-        <v>731</v>
+        <v>596</v>
       </c>
       <c r="H56" t="s">
-        <v>715</v>
+        <v>597</v>
       </c>
       <c r="I56" t="s">
         <v>25</v>
       </c>
       <c r="J56" t="s">
-        <v>732</v>
+        <v>598</v>
       </c>
       <c r="K56" t="s">
         <v>28</v>
@@ -6854,7 +7046,7 @@
         <v>28</v>
       </c>
       <c r="Q56" t="s">
-        <v>733</v>
+        <v>599</v>
       </c>
       <c r="R56" t="s">
         <v>28</v>
@@ -6865,37 +7057,31 @@
       <c r="U56" t="s">
         <v>42</v>
       </c>
-      <c r="X56" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W56" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>153489210</v>
+        <v>138816059</v>
       </c>
       <c r="B57" t="s">
-        <v>753</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>754</v>
+        <v>633</v>
+      </c>
+      <c r="C57" t="s">
+        <v>634</v>
       </c>
       <c r="E57">
-        <v>1991</v>
-      </c>
-      <c r="F57" t="s">
-        <v>757</v>
-      </c>
-      <c r="G57" t="s">
-        <v>23</v>
-      </c>
-      <c r="H57" t="s">
-        <v>755</v>
+        <v>2018</v>
       </c>
       <c r="I57" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J57" t="s">
-        <v>756</v>
+        <v>635</v>
       </c>
       <c r="K57" t="s">
         <v>28</v>
@@ -6916,7 +7102,7 @@
         <v>28</v>
       </c>
       <c r="Q57" t="s">
-        <v>564</v>
+        <v>636</v>
       </c>
       <c r="R57" t="s">
         <v>28</v>
@@ -6927,34 +7113,40 @@
       <c r="U57" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W57" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>153489230</v>
+        <v>153488800</v>
       </c>
       <c r="B58" t="s">
-        <v>765</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>766</v>
+        <v>729</v>
+      </c>
+      <c r="C58" t="s">
+        <v>730</v>
       </c>
       <c r="E58">
-        <v>2011</v>
+        <v>1999</v>
       </c>
       <c r="F58" t="s">
-        <v>770</v>
+        <v>722</v>
       </c>
       <c r="G58" t="s">
-        <v>767</v>
+        <v>731</v>
       </c>
       <c r="H58" t="s">
-        <v>768</v>
+        <v>715</v>
       </c>
       <c r="I58" t="s">
         <v>25</v>
       </c>
       <c r="J58" t="s">
-        <v>769</v>
+        <v>732</v>
       </c>
       <c r="K58" t="s">
         <v>28</v>
@@ -6975,7 +7167,7 @@
         <v>28</v>
       </c>
       <c r="Q58" t="s">
-        <v>771</v>
+        <v>733</v>
       </c>
       <c r="R58" t="s">
         <v>28</v>
@@ -6986,37 +7178,40 @@
       <c r="U58" t="s">
         <v>42</v>
       </c>
-      <c r="X58" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W58" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>174015352</v>
+        <v>153489210</v>
       </c>
       <c r="B59" t="s">
-        <v>773</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="D59" t="s">
-        <v>775</v>
+        <v>753</v>
+      </c>
+      <c r="C59" t="s">
+        <v>754</v>
       </c>
       <c r="E59">
-        <v>2012</v>
+        <v>1991</v>
       </c>
       <c r="F59" t="s">
-        <v>777</v>
+        <v>757</v>
+      </c>
+      <c r="G59" t="s">
+        <v>23</v>
       </c>
       <c r="H59" t="s">
-        <v>507</v>
+        <v>755</v>
       </c>
       <c r="I59" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J59" t="s">
-        <v>776</v>
+        <v>756</v>
       </c>
       <c r="K59" t="s">
         <v>28</v>
@@ -7037,38 +7232,29 @@
         <v>28</v>
       </c>
       <c r="Q59" t="s">
-        <v>618</v>
+        <v>564</v>
       </c>
       <c r="R59" t="s">
         <v>28</v>
       </c>
       <c r="S59" t="s">
-        <v>33</v>
-      </c>
-      <c r="T59" t="s">
-        <v>522</v>
+        <v>42</v>
       </c>
       <c r="U59" t="s">
-        <v>836</v>
-      </c>
-      <c r="V59" t="s">
-        <v>837</v>
+        <v>42</v>
       </c>
       <c r="W59" t="s">
-        <v>523</v>
-      </c>
-      <c r="X59" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>138813043</v>
       </c>
       <c r="B60" t="s">
         <v>391</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" t="s">
         <v>392</v>
       </c>
       <c r="E60">
@@ -7122,37 +7308,40 @@
       <c r="V60" t="s">
         <v>833</v>
       </c>
-      <c r="X60" t="s">
+      <c r="W60" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y60" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>153488884</v>
+        <v>138813252</v>
       </c>
       <c r="B61" t="s">
-        <v>743</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>744</v>
+        <v>476</v>
+      </c>
+      <c r="C61" t="s">
+        <v>477</v>
       </c>
       <c r="E61">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="F61" t="s">
-        <v>746</v>
+        <v>481</v>
       </c>
       <c r="G61" t="s">
-        <v>527</v>
+        <v>478</v>
       </c>
       <c r="H61" t="s">
-        <v>528</v>
+        <v>479</v>
       </c>
       <c r="I61" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J61" t="s">
-        <v>745</v>
+        <v>480</v>
       </c>
       <c r="K61" t="s">
         <v>28</v>
@@ -7173,57 +7362,48 @@
         <v>28</v>
       </c>
       <c r="Q61" t="s">
-        <v>531</v>
+        <v>325</v>
       </c>
       <c r="R61" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="S61" t="s">
         <v>33</v>
       </c>
       <c r="T61" t="s">
-        <v>522</v>
+        <v>27</v>
       </c>
       <c r="U61" t="s">
         <v>835</v>
       </c>
       <c r="V61" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="W61" t="s">
-        <v>523</v>
+        <v>853</v>
       </c>
       <c r="X61" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>138813252</v>
+        <v>138813490</v>
       </c>
       <c r="B62" t="s">
-        <v>476</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>477</v>
+        <v>519</v>
+      </c>
+      <c r="C62" t="s">
+        <v>520</v>
       </c>
       <c r="E62">
-        <v>2009</v>
-      </c>
-      <c r="F62" t="s">
-        <v>481</v>
-      </c>
-      <c r="G62" t="s">
-        <v>478</v>
-      </c>
-      <c r="H62" t="s">
-        <v>479</v>
+        <v>2014</v>
       </c>
       <c r="I62" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J62" t="s">
-        <v>480</v>
+        <v>521</v>
       </c>
       <c r="K62" t="s">
         <v>28</v>
@@ -7244,54 +7424,51 @@
         <v>28</v>
       </c>
       <c r="Q62" t="s">
-        <v>325</v>
+        <v>495</v>
       </c>
       <c r="R62" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="S62" t="s">
         <v>33</v>
       </c>
       <c r="T62" t="s">
-        <v>27</v>
+        <v>522</v>
       </c>
       <c r="U62" t="s">
         <v>835</v>
       </c>
       <c r="V62" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="W62" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="X62" t="s">
+        <v>523</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>153488688</v>
+        <v>138816975</v>
       </c>
       <c r="B63" t="s">
-        <v>712</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>713</v>
+        <v>653</v>
+      </c>
+      <c r="C63" t="s">
+        <v>654</v>
       </c>
       <c r="E63">
-        <v>2016</v>
-      </c>
-      <c r="F63" t="s">
-        <v>717</v>
-      </c>
-      <c r="G63" t="s">
-        <v>714</v>
-      </c>
-      <c r="H63" t="s">
-        <v>715</v>
+        <v>2020</v>
       </c>
       <c r="I63" t="s">
         <v>114</v>
       </c>
       <c r="J63" t="s">
-        <v>716</v>
+        <v>655</v>
       </c>
       <c r="K63" t="s">
         <v>28</v>
@@ -7300,42 +7477,48 @@
         <v>30</v>
       </c>
       <c r="M63" t="s">
+        <v>28</v>
+      </c>
+      <c r="N63" t="s">
         <v>32</v>
       </c>
       <c r="S63" t="s">
         <v>33</v>
       </c>
       <c r="T63" t="s">
-        <v>522</v>
+        <v>656</v>
       </c>
       <c r="U63" t="s">
         <v>835</v>
       </c>
       <c r="V63" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="W63" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="X63" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>138817120</v>
+        <v>138817047</v>
       </c>
       <c r="B64" t="s">
-        <v>686</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>687</v>
+        <v>663</v>
+      </c>
+      <c r="C64" t="s">
+        <v>664</v>
       </c>
       <c r="E64">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="I64" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J64" t="s">
-        <v>688</v>
+        <v>665</v>
       </c>
       <c r="K64" t="s">
         <v>28</v>
@@ -7344,22 +7527,7 @@
         <v>30</v>
       </c>
       <c r="M64" t="s">
-        <v>28</v>
-      </c>
-      <c r="N64" t="s">
-        <v>28</v>
-      </c>
-      <c r="O64" t="s">
-        <v>28</v>
-      </c>
-      <c r="P64" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>689</v>
-      </c>
-      <c r="R64" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="S64" t="s">
         <v>33</v>
@@ -7371,36 +7539,33 @@
         <v>835</v>
       </c>
       <c r="V64" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="W64" t="s">
-        <v>523</v>
+        <v>853</v>
       </c>
       <c r="X64" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>174016382</v>
+        <v>138817120</v>
       </c>
       <c r="B65" t="s">
-        <v>793</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="D65" t="s">
-        <v>795</v>
+        <v>686</v>
+      </c>
+      <c r="C65" t="s">
+        <v>687</v>
       </c>
       <c r="E65">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="I65" t="s">
         <v>25</v>
       </c>
       <c r="J65" t="s">
-        <v>796</v>
+        <v>688</v>
       </c>
       <c r="K65" t="s">
         <v>28</v>
@@ -7421,7 +7586,7 @@
         <v>28</v>
       </c>
       <c r="Q65" t="s">
-        <v>296</v>
+        <v>689</v>
       </c>
       <c r="R65" t="s">
         <v>28</v>
@@ -7436,23 +7601,26 @@
         <v>835</v>
       </c>
       <c r="V65" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="W65" t="s">
+        <v>853</v>
+      </c>
+      <c r="X65" t="s">
         <v>523</v>
       </c>
-      <c r="X65" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y65" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>138817129</v>
       </c>
       <c r="B66" t="s">
         <v>691</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" t="s">
         <v>692</v>
       </c>
       <c r="E66">
@@ -7500,28 +7668,40 @@
       <c r="V66" t="s">
         <v>829</v>
       </c>
-      <c r="X66" t="s">
+      <c r="W66" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y66" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>138813490</v>
+        <v>153488688</v>
       </c>
       <c r="B67" t="s">
-        <v>519</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>520</v>
+        <v>712</v>
+      </c>
+      <c r="C67" t="s">
+        <v>713</v>
       </c>
       <c r="E67">
-        <v>2014</v>
+        <v>2016</v>
+      </c>
+      <c r="F67" t="s">
+        <v>717</v>
+      </c>
+      <c r="G67" t="s">
+        <v>714</v>
+      </c>
+      <c r="H67" t="s">
+        <v>715</v>
       </c>
       <c r="I67" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J67" t="s">
-        <v>521</v>
+        <v>716</v>
       </c>
       <c r="K67" t="s">
         <v>28</v>
@@ -7530,22 +7710,7 @@
         <v>30</v>
       </c>
       <c r="M67" t="s">
-        <v>28</v>
-      </c>
-      <c r="N67" t="s">
-        <v>28</v>
-      </c>
-      <c r="O67" t="s">
-        <v>28</v>
-      </c>
-      <c r="P67" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>495</v>
-      </c>
-      <c r="R67" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="S67" t="s">
         <v>33</v>
@@ -7557,33 +7722,42 @@
         <v>835</v>
       </c>
       <c r="V67" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="W67" t="s">
-        <v>523</v>
+        <v>853</v>
       </c>
       <c r="X67" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>138817047</v>
+        <v>153488884</v>
       </c>
       <c r="B68" t="s">
-        <v>663</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>664</v>
+        <v>743</v>
+      </c>
+      <c r="C68" t="s">
+        <v>744</v>
       </c>
       <c r="E68">
-        <v>2018</v>
+        <v>2012</v>
+      </c>
+      <c r="F68" t="s">
+        <v>746</v>
+      </c>
+      <c r="G68" t="s">
+        <v>527</v>
+      </c>
+      <c r="H68" t="s">
+        <v>528</v>
       </c>
       <c r="I68" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J68" t="s">
-        <v>665</v>
+        <v>745</v>
       </c>
       <c r="K68" t="s">
         <v>28</v>
@@ -7592,7 +7766,22 @@
         <v>30</v>
       </c>
       <c r="M68" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="N68" t="s">
+        <v>28</v>
+      </c>
+      <c r="O68" t="s">
+        <v>28</v>
+      </c>
+      <c r="P68" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>531</v>
+      </c>
+      <c r="R68" t="s">
+        <v>28</v>
       </c>
       <c r="S68" t="s">
         <v>33</v>
@@ -7604,30 +7793,39 @@
         <v>835</v>
       </c>
       <c r="V68" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="W68" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="X68" t="s">
+        <v>523</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>138816975</v>
+        <v>174016382</v>
       </c>
       <c r="B69" t="s">
-        <v>653</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>654</v>
+        <v>793</v>
+      </c>
+      <c r="C69" t="s">
+        <v>794</v>
+      </c>
+      <c r="D69" t="s">
+        <v>795</v>
       </c>
       <c r="E69">
         <v>2020</v>
       </c>
       <c r="I69" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J69" t="s">
-        <v>655</v>
+        <v>796</v>
       </c>
       <c r="K69" t="s">
         <v>28</v>
@@ -7639,32 +7837,50 @@
         <v>28</v>
       </c>
       <c r="N69" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="O69" t="s">
+        <v>28</v>
+      </c>
+      <c r="P69" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>296</v>
+      </c>
+      <c r="R69" t="s">
+        <v>28</v>
       </c>
       <c r="S69" t="s">
         <v>33</v>
       </c>
       <c r="T69" t="s">
-        <v>656</v>
+        <v>522</v>
       </c>
       <c r="U69" t="s">
         <v>835</v>
       </c>
       <c r="V69" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="W69" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="X69" t="s">
+        <v>523</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>807</v>
       </c>
       <c r="B70" t="s">
         <v>812</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" t="s">
         <v>814</v>
       </c>
       <c r="D70" t="s">
@@ -7724,34 +7940,34 @@
       <c r="V70" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W70" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>138813496</v>
+        <v>138812557</v>
       </c>
       <c r="B71" t="s">
-        <v>525</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>526</v>
+        <v>226</v>
+      </c>
+      <c r="C71" t="s">
+        <v>227</v>
       </c>
       <c r="E71">
-        <v>2012</v>
-      </c>
-      <c r="F71" t="s">
-        <v>530</v>
+        <v>2021</v>
       </c>
       <c r="G71" t="s">
-        <v>527</v>
+        <v>228</v>
       </c>
       <c r="H71" t="s">
-        <v>528</v>
+        <v>229</v>
       </c>
       <c r="I71" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J71" t="s">
-        <v>529</v>
+        <v>230</v>
       </c>
       <c r="K71" t="s">
         <v>28</v>
@@ -7772,7 +7988,7 @@
         <v>28</v>
       </c>
       <c r="Q71" t="s">
-        <v>531</v>
+        <v>231</v>
       </c>
       <c r="R71" t="s">
         <v>28</v>
@@ -7780,17 +7996,23 @@
       <c r="S71" t="s">
         <v>42</v>
       </c>
+      <c r="T71" t="s">
+        <v>818</v>
+      </c>
       <c r="U71" t="s">
         <v>823</v>
       </c>
       <c r="V71" t="s">
-        <v>850</v>
+        <v>822</v>
+      </c>
+      <c r="W71" t="s">
+        <v>853</v>
       </c>
       <c r="X71" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>138812860</v>
       </c>
@@ -7854,34 +8076,37 @@
       <c r="V72" t="s">
         <v>822</v>
       </c>
-      <c r="X72" t="s">
+      <c r="W72" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y72" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>138812557</v>
+        <v>138812967</v>
       </c>
       <c r="B73" t="s">
-        <v>226</v>
+        <v>356</v>
       </c>
       <c r="C73" t="s">
-        <v>227</v>
+        <v>357</v>
       </c>
       <c r="E73">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G73" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="H73" t="s">
-        <v>229</v>
+        <v>359</v>
       </c>
       <c r="I73" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J73" t="s">
-        <v>230</v>
+        <v>360</v>
       </c>
       <c r="K73" t="s">
         <v>28</v>
@@ -7902,7 +8127,7 @@
         <v>28</v>
       </c>
       <c r="Q73" t="s">
-        <v>231</v>
+        <v>361</v>
       </c>
       <c r="R73" t="s">
         <v>28</v>
@@ -7920,33 +8145,39 @@
         <v>822</v>
       </c>
       <c r="W73" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>138812967</v>
+        <v>138813496</v>
       </c>
       <c r="B74" t="s">
-        <v>356</v>
+        <v>525</v>
       </c>
       <c r="C74" t="s">
-        <v>357</v>
+        <v>526</v>
       </c>
       <c r="E74">
-        <v>2020</v>
+        <v>2012</v>
+      </c>
+      <c r="F74" t="s">
+        <v>530</v>
       </c>
       <c r="G74" t="s">
-        <v>358</v>
+        <v>527</v>
       </c>
       <c r="H74" t="s">
-        <v>359</v>
+        <v>528</v>
       </c>
       <c r="I74" t="s">
         <v>25</v>
       </c>
       <c r="J74" t="s">
-        <v>360</v>
+        <v>529</v>
       </c>
       <c r="K74" t="s">
         <v>28</v>
@@ -7967,7 +8198,7 @@
         <v>28</v>
       </c>
       <c r="Q74" t="s">
-        <v>361</v>
+        <v>531</v>
       </c>
       <c r="R74" t="s">
         <v>28</v>
@@ -7975,20 +8206,20 @@
       <c r="S74" t="s">
         <v>42</v>
       </c>
-      <c r="T74" t="s">
-        <v>818</v>
-      </c>
       <c r="U74" t="s">
         <v>823</v>
       </c>
       <c r="V74" t="s">
-        <v>822</v>
-      </c>
-      <c r="X74" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
+        <v>850</v>
+      </c>
+      <c r="W74" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>153489229</v>
       </c>
@@ -8052,43 +8283,46 @@
       <c r="V75" t="s">
         <v>822</v>
       </c>
-      <c r="X75" t="s">
+      <c r="W75" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y75" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>138817053</v>
+        <v>138812505</v>
       </c>
       <c r="B76" t="s">
-        <v>667</v>
+        <v>21</v>
       </c>
       <c r="C76" t="s">
-        <v>668</v>
+        <v>22</v>
       </c>
       <c r="E76">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F76" t="s">
-        <v>673</v>
+        <v>29</v>
       </c>
       <c r="G76" t="s">
-        <v>669</v>
+        <v>23</v>
       </c>
       <c r="H76" t="s">
-        <v>670</v>
+        <v>24</v>
       </c>
       <c r="I76" t="s">
         <v>25</v>
       </c>
       <c r="J76" t="s">
-        <v>671</v>
+        <v>26</v>
       </c>
       <c r="K76" t="s">
         <v>28</v>
       </c>
       <c r="L76" t="s">
-        <v>674</v>
+        <v>30</v>
       </c>
       <c r="M76" t="s">
         <v>28</v>
@@ -8098,47 +8332,59 @@
       </c>
       <c r="O76" t="s">
         <v>28</v>
+      </c>
+      <c r="P76" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>31</v>
+      </c>
+      <c r="R76" t="s">
+        <v>32</v>
       </c>
       <c r="S76" t="s">
         <v>33</v>
       </c>
       <c r="T76" t="s">
-        <v>672</v>
+        <v>27</v>
       </c>
       <c r="U76" t="s">
         <v>33</v>
       </c>
+      <c r="W76" t="s">
+        <v>853</v>
+      </c>
       <c r="X76" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>138813177</v>
+        <v>138812526</v>
       </c>
       <c r="B77" t="s">
-        <v>450</v>
+        <v>44</v>
       </c>
       <c r="C77" t="s">
-        <v>451</v>
+        <v>45</v>
       </c>
       <c r="E77">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="F77" t="s">
-        <v>456</v>
+        <v>49</v>
       </c>
       <c r="G77" t="s">
-        <v>452</v>
+        <v>46</v>
       </c>
       <c r="H77" t="s">
-        <v>453</v>
+        <v>47</v>
       </c>
       <c r="I77" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J77" t="s">
-        <v>454</v>
+        <v>48</v>
       </c>
       <c r="K77" t="s">
         <v>28</v>
@@ -8159,51 +8405,54 @@
         <v>28</v>
       </c>
       <c r="Q77" t="s">
-        <v>457</v>
+        <v>50</v>
       </c>
       <c r="R77" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="S77" t="s">
         <v>33</v>
       </c>
       <c r="T77" t="s">
-        <v>455</v>
+        <v>27</v>
       </c>
       <c r="U77" t="s">
         <v>33</v>
       </c>
       <c r="W77" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>138813391</v>
+        <v>138812530</v>
       </c>
       <c r="B78" t="s">
-        <v>505</v>
+        <v>75</v>
       </c>
       <c r="C78" t="s">
-        <v>506</v>
+        <v>76</v>
       </c>
       <c r="E78">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="F78" t="s">
-        <v>509</v>
+        <v>79</v>
       </c>
       <c r="G78" t="s">
-        <v>157</v>
+        <v>23</v>
       </c>
       <c r="H78" t="s">
-        <v>507</v>
+        <v>77</v>
       </c>
       <c r="I78" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J78" t="s">
-        <v>508</v>
+        <v>78</v>
       </c>
       <c r="K78" t="s">
         <v>28</v>
@@ -8224,48 +8473,54 @@
         <v>28</v>
       </c>
       <c r="Q78" t="s">
-        <v>510</v>
+        <v>80</v>
       </c>
       <c r="R78" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="S78" t="s">
         <v>33</v>
       </c>
       <c r="T78" t="s">
-        <v>455</v>
+        <v>27</v>
       </c>
       <c r="U78" t="s">
         <v>33</v>
       </c>
       <c r="W78" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>138815708</v>
+        <v>138812534</v>
       </c>
       <c r="B79" t="s">
-        <v>627</v>
+        <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>628</v>
+        <v>103</v>
       </c>
       <c r="E79">
-        <v>2017</v>
+        <v>2012</v>
+      </c>
+      <c r="F79" t="s">
+        <v>107</v>
       </c>
       <c r="G79" t="s">
-        <v>629</v>
+        <v>104</v>
       </c>
       <c r="H79" t="s">
-        <v>630</v>
+        <v>105</v>
       </c>
       <c r="I79" t="s">
         <v>25</v>
       </c>
       <c r="J79" t="s">
-        <v>631</v>
+        <v>106</v>
       </c>
       <c r="K79" t="s">
         <v>28</v>
@@ -8284,6 +8539,9 @@
       </c>
       <c r="P79" t="s">
         <v>28</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>108</v>
       </c>
       <c r="R79" t="s">
         <v>32</v>
@@ -8292,42 +8550,45 @@
         <v>33</v>
       </c>
       <c r="T79" t="s">
-        <v>455</v>
+        <v>27</v>
       </c>
       <c r="U79" t="s">
         <v>33</v>
       </c>
-      <c r="X79" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W79" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>138812505</v>
+        <v>138812537</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="C80" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="E80">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="F80" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="G80" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="H80" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="I80" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J80" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="K80" t="s">
         <v>28</v>
@@ -8348,7 +8609,7 @@
         <v>28</v>
       </c>
       <c r="Q80" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="R80" t="s">
         <v>32</v>
@@ -8363,36 +8624,30 @@
         <v>33</v>
       </c>
       <c r="W80" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>138812526</v>
+        <v>138812538</v>
       </c>
       <c r="B81" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="C81" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="E81">
-        <v>2017</v>
-      </c>
-      <c r="F81" t="s">
-        <v>49</v>
-      </c>
-      <c r="G81" t="s">
-        <v>46</v>
-      </c>
-      <c r="H81" t="s">
-        <v>47</v>
+        <v>2019</v>
       </c>
       <c r="I81" t="s">
         <v>25</v>
       </c>
       <c r="J81" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="K81" t="s">
         <v>28</v>
@@ -8413,7 +8668,7 @@
         <v>28</v>
       </c>
       <c r="Q81" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="R81" t="s">
         <v>32</v>
@@ -8427,37 +8682,40 @@
       <c r="U81" t="s">
         <v>33</v>
       </c>
-      <c r="X81" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W81" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>138812530</v>
+        <v>138812539</v>
       </c>
       <c r="B82" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="C82" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="E82">
-        <v>2020</v>
+        <v>2007</v>
       </c>
       <c r="F82" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="G82" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="H82" t="s">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="I82" t="s">
         <v>25</v>
       </c>
       <c r="J82" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="K82" t="s">
         <v>28</v>
@@ -8475,10 +8733,10 @@
         <v>28</v>
       </c>
       <c r="P82" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="Q82" t="s">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="R82" t="s">
         <v>32</v>
@@ -8492,37 +8750,40 @@
       <c r="U82" t="s">
         <v>33</v>
       </c>
-      <c r="X82" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W82" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>138812534</v>
+        <v>138812541</v>
       </c>
       <c r="B83" t="s">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="C83" t="s">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="E83">
         <v>2012</v>
       </c>
       <c r="F83" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="G83" t="s">
-        <v>104</v>
+        <v>157</v>
       </c>
       <c r="H83" t="s">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="I83" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J83" t="s">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="K83" t="s">
         <v>28</v>
@@ -8543,7 +8804,7 @@
         <v>28</v>
       </c>
       <c r="Q83" t="s">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="R83" t="s">
         <v>32</v>
@@ -8557,37 +8818,40 @@
       <c r="U83" t="s">
         <v>33</v>
       </c>
+      <c r="W83" t="s">
+        <v>853</v>
+      </c>
       <c r="X83" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>138812537</v>
+        <v>138812543</v>
       </c>
       <c r="B84" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="C84" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="E84">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="F84" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="G84" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="H84" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="I84" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J84" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="K84" t="s">
         <v>28</v>
@@ -8608,7 +8872,7 @@
         <v>28</v>
       </c>
       <c r="Q84" t="s">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="R84" t="s">
         <v>32</v>
@@ -8622,28 +8886,40 @@
       <c r="U84" t="s">
         <v>33</v>
       </c>
-      <c r="X84" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W84" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>138812538</v>
+        <v>138812545</v>
       </c>
       <c r="B85" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="E85">
-        <v>2019</v>
+        <v>2011</v>
+      </c>
+      <c r="F85" t="s">
+        <v>190</v>
+      </c>
+      <c r="G85" t="s">
+        <v>187</v>
+      </c>
+      <c r="H85" t="s">
+        <v>188</v>
       </c>
       <c r="I85" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J85" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="K85" t="s">
         <v>28</v>
@@ -8664,7 +8940,7 @@
         <v>28</v>
       </c>
       <c r="Q85" t="s">
-        <v>136</v>
+        <v>191</v>
       </c>
       <c r="R85" t="s">
         <v>32</v>
@@ -8678,37 +8954,43 @@
       <c r="U85" t="s">
         <v>33</v>
       </c>
+      <c r="W85" t="s">
+        <v>853</v>
+      </c>
       <c r="X85" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>138812539</v>
+        <v>138812551</v>
       </c>
       <c r="B86" t="s">
-        <v>138</v>
+        <v>208</v>
       </c>
       <c r="C86" t="s">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="E86">
-        <v>2007</v>
+        <v>2018</v>
       </c>
       <c r="F86" t="s">
-        <v>143</v>
+        <v>213</v>
       </c>
       <c r="G86" t="s">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="H86" t="s">
-        <v>141</v>
+        <v>211</v>
       </c>
       <c r="I86" t="s">
         <v>25</v>
       </c>
       <c r="J86" t="s">
-        <v>142</v>
+        <v>212</v>
       </c>
       <c r="K86" t="s">
         <v>28</v>
@@ -8729,7 +9011,7 @@
         <v>144</v>
       </c>
       <c r="Q86" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="R86" t="s">
         <v>32</v>
@@ -8743,37 +9025,37 @@
       <c r="U86" t="s">
         <v>33</v>
       </c>
-      <c r="X86" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W86" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>138812541</v>
+        <v>138812561</v>
       </c>
       <c r="B87" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="C87" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="E87">
-        <v>2012</v>
-      </c>
-      <c r="F87" t="s">
-        <v>160</v>
+        <v>2022</v>
       </c>
       <c r="G87" t="s">
-        <v>157</v>
+        <v>249</v>
       </c>
       <c r="H87" t="s">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="I87" t="s">
         <v>114</v>
       </c>
       <c r="J87" t="s">
-        <v>159</v>
+        <v>251</v>
       </c>
       <c r="K87" t="s">
         <v>28</v>
@@ -8794,7 +9076,7 @@
         <v>28</v>
       </c>
       <c r="Q87" t="s">
-        <v>161</v>
+        <v>41</v>
       </c>
       <c r="R87" t="s">
         <v>32</v>
@@ -8809,36 +9091,36 @@
         <v>33</v>
       </c>
       <c r="W87" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="X87" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>138812543</v>
+        <v>138812576</v>
       </c>
       <c r="B88" t="s">
-        <v>170</v>
+        <v>253</v>
       </c>
       <c r="C88" t="s">
-        <v>171</v>
+        <v>254</v>
       </c>
       <c r="E88">
-        <v>2021</v>
-      </c>
-      <c r="F88" t="s">
-        <v>175</v>
+        <v>2020</v>
       </c>
       <c r="G88" t="s">
-        <v>172</v>
+        <v>255</v>
       </c>
       <c r="H88" t="s">
-        <v>173</v>
+        <v>256</v>
       </c>
       <c r="I88" t="s">
         <v>25</v>
       </c>
       <c r="J88" t="s">
-        <v>174</v>
+        <v>257</v>
       </c>
       <c r="K88" t="s">
         <v>28</v>
@@ -8859,7 +9141,7 @@
         <v>28</v>
       </c>
       <c r="Q88" t="s">
-        <v>176</v>
+        <v>258</v>
       </c>
       <c r="R88" t="s">
         <v>32</v>
@@ -8873,37 +9155,40 @@
       <c r="U88" t="s">
         <v>33</v>
       </c>
-      <c r="X88" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W88" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>138812545</v>
+        <v>138812636</v>
       </c>
       <c r="B89" t="s">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="C89" t="s">
-        <v>186</v>
+        <v>276</v>
       </c>
       <c r="E89">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="F89" t="s">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="G89" t="s">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="H89" t="s">
-        <v>188</v>
+        <v>278</v>
       </c>
       <c r="I89" t="s">
         <v>114</v>
       </c>
       <c r="J89" t="s">
-        <v>189</v>
+        <v>279</v>
       </c>
       <c r="K89" t="s">
         <v>28</v>
@@ -8924,7 +9209,7 @@
         <v>28</v>
       </c>
       <c r="Q89" t="s">
-        <v>191</v>
+        <v>281</v>
       </c>
       <c r="R89" t="s">
         <v>32</v>
@@ -8939,39 +9224,36 @@
         <v>33</v>
       </c>
       <c r="W89" t="s">
-        <v>118</v>
-      </c>
-      <c r="X89" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>138812551</v>
+        <v>138812641</v>
       </c>
       <c r="B90" t="s">
-        <v>208</v>
+        <v>282</v>
       </c>
       <c r="C90" t="s">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="E90">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F90" t="s">
-        <v>213</v>
+        <v>287</v>
       </c>
       <c r="G90" t="s">
-        <v>210</v>
+        <v>284</v>
       </c>
       <c r="H90" t="s">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="I90" t="s">
         <v>25</v>
       </c>
       <c r="J90" t="s">
-        <v>212</v>
+        <v>286</v>
       </c>
       <c r="K90" t="s">
         <v>28</v>
@@ -8989,10 +9271,10 @@
         <v>28</v>
       </c>
       <c r="P90" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="Q90" t="s">
-        <v>214</v>
+        <v>288</v>
       </c>
       <c r="R90" t="s">
         <v>32</v>
@@ -9006,34 +9288,40 @@
       <c r="U90" t="s">
         <v>33</v>
       </c>
-      <c r="X90" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W90" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>138812561</v>
+        <v>138812831</v>
       </c>
       <c r="B91" t="s">
-        <v>247</v>
+        <v>319</v>
       </c>
       <c r="C91" t="s">
-        <v>248</v>
+        <v>320</v>
       </c>
       <c r="E91">
-        <v>2022</v>
+        <v>2016</v>
+      </c>
+      <c r="F91" t="s">
+        <v>324</v>
       </c>
       <c r="G91" t="s">
-        <v>249</v>
+        <v>321</v>
       </c>
       <c r="H91" t="s">
-        <v>250</v>
+        <v>322</v>
       </c>
       <c r="I91" t="s">
         <v>114</v>
       </c>
       <c r="J91" t="s">
-        <v>251</v>
+        <v>323</v>
       </c>
       <c r="K91" t="s">
         <v>28</v>
@@ -9054,7 +9342,7 @@
         <v>28</v>
       </c>
       <c r="Q91" t="s">
-        <v>41</v>
+        <v>325</v>
       </c>
       <c r="R91" t="s">
         <v>32</v>
@@ -9069,33 +9357,39 @@
         <v>33</v>
       </c>
       <c r="W91" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="X91" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>138812576</v>
+        <v>138812994</v>
       </c>
       <c r="B92" t="s">
-        <v>253</v>
+        <v>363</v>
       </c>
       <c r="C92" t="s">
-        <v>254</v>
+        <v>364</v>
       </c>
       <c r="E92">
-        <v>2020</v>
+        <v>2022</v>
+      </c>
+      <c r="F92" t="s">
+        <v>368</v>
       </c>
       <c r="G92" t="s">
-        <v>255</v>
+        <v>365</v>
       </c>
       <c r="H92" t="s">
-        <v>256</v>
+        <v>366</v>
       </c>
       <c r="I92" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J92" t="s">
-        <v>257</v>
+        <v>367</v>
       </c>
       <c r="K92" t="s">
         <v>28</v>
@@ -9113,10 +9407,10 @@
         <v>28</v>
       </c>
       <c r="P92" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="Q92" t="s">
-        <v>258</v>
+        <v>369</v>
       </c>
       <c r="R92" t="s">
         <v>32</v>
@@ -9130,37 +9424,43 @@
       <c r="U92" t="s">
         <v>33</v>
       </c>
+      <c r="W92" t="s">
+        <v>853</v>
+      </c>
       <c r="X92" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>138812636</v>
+        <v>138813046</v>
       </c>
       <c r="B93" t="s">
-        <v>275</v>
+        <v>398</v>
       </c>
       <c r="C93" t="s">
-        <v>276</v>
+        <v>399</v>
       </c>
       <c r="E93">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="F93" t="s">
-        <v>280</v>
+        <v>402</v>
       </c>
       <c r="G93" t="s">
-        <v>277</v>
+        <v>358</v>
       </c>
       <c r="H93" t="s">
-        <v>278</v>
+        <v>400</v>
       </c>
       <c r="I93" t="s">
         <v>114</v>
       </c>
       <c r="J93" t="s">
-        <v>279</v>
+        <v>401</v>
       </c>
       <c r="K93" t="s">
         <v>28</v>
@@ -9181,7 +9481,7 @@
         <v>28</v>
       </c>
       <c r="Q93" t="s">
-        <v>281</v>
+        <v>403</v>
       </c>
       <c r="R93" t="s">
         <v>32</v>
@@ -9195,34 +9495,40 @@
       <c r="U93" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W93" t="s">
+        <v>853</v>
+      </c>
+      <c r="X93" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>138812641</v>
+        <v>138813061</v>
       </c>
       <c r="B94" t="s">
-        <v>282</v>
+        <v>405</v>
       </c>
       <c r="C94" t="s">
-        <v>283</v>
+        <v>406</v>
       </c>
       <c r="E94">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="F94" t="s">
-        <v>287</v>
+        <v>410</v>
       </c>
       <c r="G94" t="s">
-        <v>284</v>
+        <v>407</v>
       </c>
       <c r="H94" t="s">
-        <v>285</v>
+        <v>408</v>
       </c>
       <c r="I94" t="s">
         <v>25</v>
       </c>
       <c r="J94" t="s">
-        <v>286</v>
+        <v>409</v>
       </c>
       <c r="K94" t="s">
         <v>28</v>
@@ -9243,7 +9549,7 @@
         <v>28</v>
       </c>
       <c r="Q94" t="s">
-        <v>288</v>
+        <v>411</v>
       </c>
       <c r="R94" t="s">
         <v>32</v>
@@ -9257,37 +9563,40 @@
       <c r="U94" t="s">
         <v>33</v>
       </c>
-      <c r="X94" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W94" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>138812831</v>
+        <v>138813074</v>
       </c>
       <c r="B95" t="s">
-        <v>319</v>
+        <v>421</v>
       </c>
       <c r="C95" t="s">
-        <v>320</v>
+        <v>422</v>
       </c>
       <c r="E95">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F95" t="s">
-        <v>324</v>
+        <v>425</v>
       </c>
       <c r="G95" t="s">
-        <v>321</v>
+        <v>187</v>
       </c>
       <c r="H95" t="s">
-        <v>322</v>
+        <v>423</v>
       </c>
       <c r="I95" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J95" t="s">
-        <v>323</v>
+        <v>424</v>
       </c>
       <c r="K95" t="s">
         <v>28</v>
@@ -9308,7 +9617,7 @@
         <v>28</v>
       </c>
       <c r="Q95" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="R95" t="s">
         <v>32</v>
@@ -9323,36 +9632,39 @@
         <v>33</v>
       </c>
       <c r="W95" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>138812994</v>
+        <v>138813088</v>
       </c>
       <c r="B96" t="s">
-        <v>363</v>
+        <v>427</v>
       </c>
       <c r="C96" t="s">
-        <v>364</v>
+        <v>428</v>
       </c>
       <c r="E96">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F96" t="s">
-        <v>368</v>
+        <v>432</v>
       </c>
       <c r="G96" t="s">
-        <v>365</v>
+        <v>429</v>
       </c>
       <c r="H96" t="s">
-        <v>366</v>
+        <v>430</v>
       </c>
       <c r="I96" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J96" t="s">
-        <v>367</v>
+        <v>431</v>
       </c>
       <c r="K96" t="s">
         <v>28</v>
@@ -9370,10 +9682,10 @@
         <v>28</v>
       </c>
       <c r="P96" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="Q96" t="s">
-        <v>369</v>
+        <v>433</v>
       </c>
       <c r="R96" t="s">
         <v>32</v>
@@ -9388,39 +9700,39 @@
         <v>33</v>
       </c>
       <c r="W96" t="s">
-        <v>118</v>
-      </c>
-      <c r="X96" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>138813046</v>
+        <v>138813107</v>
       </c>
       <c r="B97" t="s">
-        <v>398</v>
+        <v>435</v>
       </c>
       <c r="C97" t="s">
-        <v>399</v>
+        <v>436</v>
       </c>
       <c r="E97">
         <v>2022</v>
       </c>
       <c r="F97" t="s">
-        <v>402</v>
+        <v>439</v>
       </c>
       <c r="G97" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="H97" t="s">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="I97" t="s">
         <v>114</v>
       </c>
       <c r="J97" t="s">
-        <v>401</v>
+        <v>438</v>
       </c>
       <c r="K97" t="s">
         <v>28</v>
@@ -9441,7 +9753,7 @@
         <v>28</v>
       </c>
       <c r="Q97" t="s">
-        <v>403</v>
+        <v>440</v>
       </c>
       <c r="R97" t="s">
         <v>32</v>
@@ -9456,36 +9768,39 @@
         <v>33</v>
       </c>
       <c r="W97" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="X97" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>138813061</v>
+        <v>138813108</v>
       </c>
       <c r="B98" t="s">
-        <v>405</v>
+        <v>442</v>
       </c>
       <c r="C98" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="E98">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="F98" t="s">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="G98" t="s">
-        <v>407</v>
+        <v>444</v>
       </c>
       <c r="H98" t="s">
-        <v>408</v>
+        <v>445</v>
       </c>
       <c r="I98" t="s">
         <v>25</v>
       </c>
       <c r="J98" t="s">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="K98" t="s">
         <v>28</v>
@@ -9503,10 +9818,10 @@
         <v>28</v>
       </c>
       <c r="P98" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="Q98" t="s">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="R98" t="s">
         <v>32</v>
@@ -9520,37 +9835,40 @@
       <c r="U98" t="s">
         <v>33</v>
       </c>
-      <c r="X98" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W98" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>138813074</v>
+        <v>138813177</v>
       </c>
       <c r="B99" t="s">
-        <v>421</v>
+        <v>450</v>
       </c>
       <c r="C99" t="s">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="E99">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="F99" t="s">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="G99" t="s">
-        <v>187</v>
+        <v>452</v>
       </c>
       <c r="H99" t="s">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="I99" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J99" t="s">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="K99" t="s">
         <v>28</v>
@@ -9571,51 +9889,51 @@
         <v>28</v>
       </c>
       <c r="Q99" t="s">
-        <v>426</v>
+        <v>457</v>
       </c>
       <c r="R99" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="S99" t="s">
         <v>33</v>
       </c>
       <c r="T99" t="s">
-        <v>27</v>
+        <v>455</v>
       </c>
       <c r="U99" t="s">
         <v>33</v>
       </c>
+      <c r="W99" t="s">
+        <v>853</v>
+      </c>
       <c r="X99" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>138813088</v>
+        <v>138813183</v>
       </c>
       <c r="B100" t="s">
-        <v>427</v>
+        <v>458</v>
       </c>
       <c r="C100" t="s">
-        <v>428</v>
+        <v>459</v>
       </c>
       <c r="E100">
-        <v>2023</v>
-      </c>
-      <c r="F100" t="s">
-        <v>432</v>
+        <v>2019</v>
       </c>
       <c r="G100" t="s">
-        <v>429</v>
+        <v>90</v>
       </c>
       <c r="H100" t="s">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="I100" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J100" t="s">
-        <v>431</v>
+        <v>461</v>
       </c>
       <c r="K100" t="s">
         <v>28</v>
@@ -9636,7 +9954,7 @@
         <v>28</v>
       </c>
       <c r="Q100" t="s">
-        <v>433</v>
+        <v>462</v>
       </c>
       <c r="R100" t="s">
         <v>32</v>
@@ -9650,37 +9968,37 @@
       <c r="U100" t="s">
         <v>33</v>
       </c>
+      <c r="W100" t="s">
+        <v>853</v>
+      </c>
       <c r="X100" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>138813107</v>
+        <v>138813257</v>
       </c>
       <c r="B101" t="s">
-        <v>435</v>
+        <v>482</v>
       </c>
       <c r="C101" t="s">
-        <v>436</v>
+        <v>483</v>
       </c>
       <c r="E101">
-        <v>2022</v>
-      </c>
-      <c r="F101" t="s">
-        <v>439</v>
+        <v>2011</v>
       </c>
       <c r="G101" t="s">
-        <v>328</v>
+        <v>484</v>
       </c>
       <c r="H101" t="s">
-        <v>437</v>
+        <v>485</v>
       </c>
       <c r="I101" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J101" t="s">
-        <v>438</v>
+        <v>486</v>
       </c>
       <c r="K101" t="s">
         <v>28</v>
@@ -9698,10 +10016,10 @@
         <v>28</v>
       </c>
       <c r="P101" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="Q101" t="s">
-        <v>440</v>
+        <v>487</v>
       </c>
       <c r="R101" t="s">
         <v>32</v>
@@ -9716,36 +10034,39 @@
         <v>33</v>
       </c>
       <c r="W101" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>138813108</v>
+        <v>138813391</v>
       </c>
       <c r="B102" t="s">
-        <v>442</v>
+        <v>505</v>
       </c>
       <c r="C102" t="s">
-        <v>443</v>
+        <v>506</v>
       </c>
       <c r="E102">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="F102" t="s">
-        <v>447</v>
+        <v>509</v>
       </c>
       <c r="G102" t="s">
-        <v>444</v>
+        <v>157</v>
       </c>
       <c r="H102" t="s">
-        <v>445</v>
+        <v>507</v>
       </c>
       <c r="I102" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J102" t="s">
-        <v>446</v>
+        <v>508</v>
       </c>
       <c r="K102" t="s">
         <v>28</v>
@@ -9763,51 +10084,54 @@
         <v>28</v>
       </c>
       <c r="P102" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="Q102" t="s">
-        <v>448</v>
+        <v>510</v>
       </c>
       <c r="R102" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="S102" t="s">
         <v>33</v>
       </c>
       <c r="T102" t="s">
-        <v>27</v>
+        <v>455</v>
       </c>
       <c r="U102" t="s">
         <v>33</v>
       </c>
+      <c r="W102" t="s">
+        <v>853</v>
+      </c>
       <c r="X102" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A103">
-        <v>138813183</v>
+        <v>138813683</v>
       </c>
       <c r="B103" t="s">
-        <v>458</v>
+        <v>559</v>
       </c>
       <c r="C103" t="s">
-        <v>459</v>
+        <v>560</v>
       </c>
       <c r="E103">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G103" t="s">
-        <v>90</v>
+        <v>561</v>
       </c>
       <c r="H103" t="s">
-        <v>460</v>
+        <v>562</v>
       </c>
       <c r="I103" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J103" t="s">
-        <v>461</v>
+        <v>563</v>
       </c>
       <c r="K103" t="s">
         <v>28</v>
@@ -9828,7 +10152,7 @@
         <v>28</v>
       </c>
       <c r="Q103" t="s">
-        <v>462</v>
+        <v>564</v>
       </c>
       <c r="R103" t="s">
         <v>32</v>
@@ -9843,33 +10167,36 @@
         <v>33</v>
       </c>
       <c r="W103" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A104">
-        <v>138813257</v>
+        <v>138814610</v>
       </c>
       <c r="B104" t="s">
-        <v>482</v>
+        <v>581</v>
       </c>
       <c r="C104" t="s">
-        <v>483</v>
+        <v>582</v>
       </c>
       <c r="E104">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="G104" t="s">
-        <v>484</v>
+        <v>583</v>
       </c>
       <c r="H104" t="s">
-        <v>485</v>
+        <v>584</v>
       </c>
       <c r="I104" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J104" t="s">
-        <v>486</v>
+        <v>585</v>
       </c>
       <c r="K104" t="s">
         <v>28</v>
@@ -9887,10 +10214,10 @@
         <v>28</v>
       </c>
       <c r="P104" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="Q104" t="s">
-        <v>487</v>
+        <v>586</v>
       </c>
       <c r="R104" t="s">
         <v>32</v>
@@ -9904,34 +10231,37 @@
       <c r="U104" t="s">
         <v>33</v>
       </c>
+      <c r="W104" t="s">
+        <v>853</v>
+      </c>
       <c r="X104" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A105">
-        <v>138813683</v>
+        <v>138814623</v>
       </c>
       <c r="B105" t="s">
-        <v>559</v>
+        <v>588</v>
       </c>
       <c r="C105" t="s">
-        <v>560</v>
+        <v>589</v>
       </c>
       <c r="E105">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="G105" t="s">
-        <v>561</v>
+        <v>590</v>
       </c>
       <c r="H105" t="s">
-        <v>562</v>
+        <v>591</v>
       </c>
       <c r="I105" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="J105" t="s">
-        <v>563</v>
+        <v>592</v>
       </c>
       <c r="K105" t="s">
         <v>28</v>
@@ -9952,7 +10282,7 @@
         <v>28</v>
       </c>
       <c r="Q105" t="s">
-        <v>564</v>
+        <v>593</v>
       </c>
       <c r="R105" t="s">
         <v>32</v>
@@ -9966,34 +10296,28 @@
       <c r="U105" t="s">
         <v>33</v>
       </c>
-      <c r="X105" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W105" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A106">
-        <v>138814610</v>
+        <v>138814805</v>
       </c>
       <c r="B106" t="s">
-        <v>581</v>
+        <v>608</v>
       </c>
       <c r="C106" t="s">
-        <v>582</v>
-      </c>
-      <c r="E106">
-        <v>2024</v>
-      </c>
-      <c r="G106" t="s">
-        <v>583</v>
+        <v>609</v>
       </c>
       <c r="H106" t="s">
-        <v>584</v>
+        <v>610</v>
       </c>
       <c r="I106" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J106" t="s">
-        <v>585</v>
+        <v>611</v>
       </c>
       <c r="K106" t="s">
         <v>28</v>
@@ -10014,7 +10338,7 @@
         <v>28</v>
       </c>
       <c r="Q106" t="s">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="R106" t="s">
         <v>32</v>
@@ -10029,33 +10353,36 @@
         <v>33</v>
       </c>
       <c r="W106" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
+        <v>853</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A107">
-        <v>138814623</v>
+        <v>138815708</v>
       </c>
       <c r="B107" t="s">
-        <v>588</v>
+        <v>627</v>
       </c>
       <c r="C107" t="s">
-        <v>589</v>
+        <v>628</v>
       </c>
       <c r="E107">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="G107" t="s">
-        <v>590</v>
+        <v>629</v>
       </c>
       <c r="H107" t="s">
-        <v>591</v>
+        <v>630</v>
       </c>
       <c r="I107" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="J107" t="s">
-        <v>592</v>
+        <v>631</v>
       </c>
       <c r="K107" t="s">
         <v>28</v>
@@ -10074,9 +10401,6 @@
       </c>
       <c r="P107" t="s">
         <v>28</v>
-      </c>
-      <c r="Q107" t="s">
-        <v>593</v>
       </c>
       <c r="R107" t="s">
         <v>32</v>
@@ -10085,30 +10409,36 @@
         <v>33</v>
       </c>
       <c r="T107" t="s">
-        <v>27</v>
+        <v>455</v>
       </c>
       <c r="U107" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W107" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A108">
-        <v>138814805</v>
+        <v>138816961</v>
       </c>
       <c r="B108" t="s">
-        <v>608</v>
+        <v>649</v>
       </c>
       <c r="C108" t="s">
-        <v>609</v>
-      </c>
-      <c r="H108" t="s">
-        <v>610</v>
+        <v>650</v>
+      </c>
+      <c r="E108">
+        <v>2018</v>
       </c>
       <c r="I108" t="s">
         <v>25</v>
       </c>
       <c r="J108" t="s">
-        <v>611</v>
+        <v>651</v>
       </c>
       <c r="K108" t="s">
         <v>28</v>
@@ -10129,7 +10459,7 @@
         <v>28</v>
       </c>
       <c r="Q108" t="s">
-        <v>612</v>
+        <v>198</v>
       </c>
       <c r="R108" t="s">
         <v>32</v>
@@ -10143,34 +10473,46 @@
       <c r="U108" t="s">
         <v>33</v>
       </c>
-      <c r="X108" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W108" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A109">
-        <v>138816961</v>
+        <v>138817053</v>
       </c>
       <c r="B109" t="s">
-        <v>649</v>
+        <v>667</v>
       </c>
       <c r="C109" t="s">
-        <v>650</v>
+        <v>668</v>
       </c>
       <c r="E109">
-        <v>2018</v>
+        <v>2020</v>
+      </c>
+      <c r="F109" t="s">
+        <v>673</v>
+      </c>
+      <c r="G109" t="s">
+        <v>669</v>
+      </c>
+      <c r="H109" t="s">
+        <v>670</v>
       </c>
       <c r="I109" t="s">
         <v>25</v>
       </c>
       <c r="J109" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="K109" t="s">
         <v>28</v>
       </c>
       <c r="L109" t="s">
-        <v>30</v>
+        <v>674</v>
       </c>
       <c r="M109" t="s">
         <v>28</v>
@@ -10180,30 +10522,24 @@
       </c>
       <c r="O109" t="s">
         <v>28</v>
-      </c>
-      <c r="P109" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>198</v>
-      </c>
-      <c r="R109" t="s">
-        <v>32</v>
       </c>
       <c r="S109" t="s">
         <v>33</v>
       </c>
       <c r="T109" t="s">
-        <v>27</v>
+        <v>672</v>
       </c>
       <c r="U109" t="s">
         <v>33</v>
       </c>
-      <c r="X109" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W109" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>138817074</v>
       </c>
@@ -10255,11 +10591,14 @@
       <c r="U110" t="s">
         <v>33</v>
       </c>
-      <c r="X110" t="s">
+      <c r="W110" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y110" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>138817087</v>
       </c>
@@ -10311,11 +10650,14 @@
       <c r="U111" t="s">
         <v>33</v>
       </c>
-      <c r="X111" t="s">
+      <c r="W111" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y111" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>138817149</v>
       </c>
@@ -10367,11 +10709,14 @@
       <c r="U112" t="s">
         <v>33</v>
       </c>
-      <c r="X112" t="s">
+      <c r="W112" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y112" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>138817189</v>
       </c>
@@ -10423,11 +10768,14 @@
       <c r="U113" t="s">
         <v>33</v>
       </c>
-      <c r="X113" t="s">
+      <c r="W113" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y113" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>153488641</v>
       </c>
@@ -10488,11 +10836,14 @@
       <c r="U114" t="s">
         <v>33</v>
       </c>
-      <c r="X114" t="s">
+      <c r="W114" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y114" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>153488770</v>
       </c>
@@ -10553,11 +10904,14 @@
       <c r="U115" t="s">
         <v>33</v>
       </c>
-      <c r="X115" t="s">
+      <c r="W115" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y115" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>153488812</v>
       </c>
@@ -10618,11 +10972,14 @@
       <c r="U116" t="s">
         <v>33</v>
       </c>
-      <c r="X116" t="s">
+      <c r="W116" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y116" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>153489098</v>
       </c>
@@ -10683,11 +11040,14 @@
       <c r="U117" t="s">
         <v>33</v>
       </c>
-      <c r="X117" t="s">
+      <c r="W117" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y117" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>174016126</v>
       </c>
@@ -10748,11 +11108,14 @@
       <c r="U118" t="s">
         <v>33</v>
       </c>
-      <c r="X118" t="s">
+      <c r="W118" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y118" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>174016379</v>
       </c>
@@ -10813,11 +11176,14 @@
       <c r="U119" t="s">
         <v>33</v>
       </c>
-      <c r="X119" t="s">
+      <c r="W119" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y119" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>174017017</v>
       </c>
@@ -10878,13 +11244,18 @@
       <c r="U120" t="s">
         <v>33</v>
       </c>
-      <c r="X120" t="s">
+      <c r="W120" t="s">
+        <v>853</v>
+      </c>
+      <c r="Y120" t="s">
         <v>805</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X59">
-    <sortCondition ref="B2:B59"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB138">
+    <sortCondition descending="1" ref="U2:U138"/>
+    <sortCondition descending="1" ref="W2:W138"/>
+    <sortCondition ref="A2:A138"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
